--- a/PTBR-COM-PORTRAIT/Lang/PTBR/Dialog/Drama/kettle.xlsx
+++ b/PTBR-COM-PORTRAIT/Lang/PTBR/Dialog/Drama/kettle.xlsx
@@ -478,7 +478,7 @@
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="A1:IX451"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="0" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="8.85" customWidth="1" style="20" min="1" max="1"/>
     <col width="19.85" customWidth="1" style="20" min="2" max="2"/>
@@ -588,9 +588,9 @@
           <t>Can you hear the ancient words the wind whispers? I wander this world to learn the story of the wind.</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>Você pode ouvir as palavras antigas que o vento sussurra? Eu vagueio por este mundo para aprender a história do vento.</t>
+      <c r="L8" s="20" t="inlineStr">
+        <is>
+          <t>Consegue ouvir as palavras antigas que o vento sussurra? Eu percorro este mundo para aprender a história do vento.</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
           <t>I have some questions.</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="L10" s="20" t="inlineStr">
         <is>
           <t>Tenho algumas perguntas.</t>
         </is>
@@ -678,9 +678,9 @@
           <t>How can I help you?</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>Como posso ajudar você?</t>
+      <c r="L15" s="20" t="inlineStr">
+        <is>
+          <t>Como posso ajudar?</t>
         </is>
       </c>
     </row>
@@ -708,9 +708,9 @@
           <t>About magic stones</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>Sobre as pedras mágicas</t>
+      <c r="L16" s="20" t="inlineStr">
+        <is>
+          <t>Sobre pedras mágicas</t>
         </is>
       </c>
     </row>
@@ -743,9 +743,9 @@
           <t>About copy shop</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>Sobre a copiadora</t>
+      <c r="L17" s="20" t="inlineStr">
+        <is>
+          <t>Sobre a loja de cópias</t>
         </is>
       </c>
     </row>
@@ -773,7 +773,7 @@
           <t>(Back)</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="L18" s="20" t="inlineStr">
         <is>
           <t>(Voltar)</t>
         </is>
@@ -816,13 +816,11 @@
 One to the ancient royal family, one to the steel dragon, and one to the corrupted necromancer.</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>Algumas lendas sobre as pedras mágicas estão nos antigos manuscritos da Biblioteca Real de Palmia._x000D_
-_x000D_
-Diz-se que Palmia já possuiu três poderosas pedras mágicas: a Pedra do Rei, a Pedra do Sábio e a Pedra do Tolo. Essas pedras trouxeram prosperidade ao reino, mas foram enviadas para selar um segredo para sempre durante o reinado do Rei Zashim. Elas foram confiadas às criaturas mais poderosas e malignas._x000D_
-_x000D_
-Uma à antiga família real, uma ao dragão de aço e uma ao necromante corrompido.</t>
+      <c r="L22" s="20" t="inlineStr">
+        <is>
+          <t>Algumas lendas sobre pedras mágicas repousam nos manuscritos antigos da Biblioteca Real de Palmia.
+Dizem que Palmia um dia possuiu três poderosas pedras mágicas: a Pedra do Rei, a Pedra do Sábio e a Pedra do Tolo. Essas pedras trouxeram prosperidade ao reino, mas foram enviadas para selar um segredo para sempre no reinado do rei Zashim. Foram confiadas aos seres mais poderosos e malignos.
+Uma à família real antiga, uma ao dragão de aço, e uma ao necromante corrompido.</t>
         </is>
       </c>
     </row>
@@ -842,11 +840,10 @@
 Perhaps, one day, an adventurer like you might be the one to solve this mystery.</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>O que aconteceu com as pedras e com o segredo que o Rei Zashim tentou proteger permanece um mistério desde então. Muitos estudiosos e alquimistas tentaram descobrir a verdade, mas as respostas são tão ilusórias quanto a areia levada pelo vento._x000D_
-_x000D_
-Talvez, um dia, um aventureiro como você seja aquele que resolverá esse mistério.</t>
+      <c r="L23" s="20" t="inlineStr">
+        <is>
+          <t>O que aconteceu com as pedras e com o segredo que o rei Zashim tentava proteger permanece mistério desde então. Muitos eruditos e alquimistas tentaram desvendar a verdade, mas as respostas são tão esquivas quanto areia levada pelo vento.
+Talvez, um dia, um aventureiro como você seja quem resolva este mistério.</t>
         </is>
       </c>
     </row>
@@ -880,11 +877,10 @@
 Ancient alchemy has techniques for replicating the properties of materials. While it's not possible to duplicate every item, I can replicate items you've actually crafted or seeds, for instance.</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>Minha copiadora? Sim, comecei isso para ajudá-lo em suas aventuras._x000D_
-_x000D_
-A antiga alquimia possui técnicas para replicar as propriedades dos materiais. Embora não seja possível duplicar todos os itens, posso replicar itens que você já tenha criado ou sementes, por exemplo.</t>
+      <c r="L27" s="20" t="inlineStr">
+        <is>
+          <t>Minha loja de cópias? Sim, comecei isto para ajudar vocês nas aventuras.
+A alquimia antiga tem técnicas para replicar as propriedades dos materiais. Embora não seja possível duplicar todo item, posso replicar itens que você realmente fabricou ou sementes, por exemplo.</t>
         </is>
       </c>
     </row>
@@ -904,11 +900,10 @@
 By the way, the maximum number of items I can duplicate and sell depends on the scale of my shop. I hate to say it, but if you need more items duplicated, you can invest in my shop.</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>Se você tem um item que deseja duplicar, deixe-o comigo. Pode levar algum tempo, mas tentarei criar cópias regularmente para você._x000D_
-_x000D_
-Ah, e o número máximo de itens que posso duplicar e vender depende do tamanho da minha loja. Odeio dizer isso, mas se precisar de mais itens duplicados, você pode investir na minha loja.</t>
+      <c r="L28" s="20" t="inlineStr">
+        <is>
+          <t>Se tiver um item que queira duplicar, deixe comigo. Pode levar algum tempo, mas tentarei criar cópias regularmente para você.
+Aliás, o número máximo de itens que posso duplicar e vender depende do porte da minha loja. É com tristeza que digo, mas se precisar de mais itens duplicados, você pode investir na minha loja.</t>
         </is>
       </c>
     </row>
@@ -964,9 +959,9 @@
           <t>You seem down, Loytel. Is anything troubling you?</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Você parece abatida, Loytel. Algo está te incomodando?  </t>
+      <c r="L34" s="20" t="inlineStr">
+        <is>
+          <t>Você parece abatido, Loytel. Algo te perturba?</t>
         </is>
       </c>
     </row>
@@ -989,9 +984,9 @@
           <t xml:space="preserve">Kettle, your apprentice is quite a difficult child... </t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Kettle, sua aprendiz é uma criança bastante difícil...  </t>
+      <c r="L35" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kettle, sua aprendiza é uma criança bem difícil... </t>
         </is>
       </c>
     </row>
@@ -1009,9 +1004,9 @@
           <t xml:space="preserve">Apprentice? Ah, Quruitzia is not my apprentice. In fact, she despises alchemy. </t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Aprendiz? Ah, Quruitzia não é minha aprendiz. Na verdade, ela despreza a alquimia.  </t>
+      <c r="L36" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aprendiza? Ah, a Quruitzia não é minha aprendiza. Na verdade, ela detesta alquimia. </t>
         </is>
       </c>
     </row>
@@ -1034,9 +1029,9 @@
           <t>Oh? Why is that?</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Oh? Por quê?  </t>
+      <c r="L37" s="20" t="inlineStr">
+        <is>
+          <t>Oh? Por quê?</t>
         </is>
       </c>
     </row>
@@ -1054,9 +1049,9 @@
           <t xml:space="preserve">Because her mother was an alchemist. </t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Porque a mãe dela era uma alquimista.  </t>
+      <c r="L38" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Porque a mãe dela era alquimista. </t>
         </is>
       </c>
     </row>
@@ -1079,7 +1074,7 @@
           <t xml:space="preserve">... </t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="L39" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">... </t>
         </is>
@@ -1113,11 +1108,10 @@
 The superstitious villagers shunned her, calling her a witch. And being the witch’s daughter, Quruitzia was always ostracized by other children. Her naturally different-colored eyes were feared as "cursed eyes". </t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A mãe de Quruitzia... ela foi uma grande amiga minha. Uma alquimista em uma pequena vila, uma estudiosa extremamente dedicada. Mas, como muitas vezes acontece, os aldeões não a compreendiam.  _x000D_
-_x000D_
-Os aldeões supersticiosos a rejeitaram, chamando-a de bruxa. E, sendo a filha da bruxa, Quruitzia sempre foi excluída pelas outras crianças. Seus olhos naturalmente de cores diferentes eram temidos como 'olhos amaldiçoados'.  </t>
+      <c r="L41" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A mãe de Quruitzia era uma amiga querida minha. Alquimista de uma vilazinha, uma erudita devotada de verdade. Mas, como muitas vezes acontece, os aldeões não a entendiam.
+Os aldeões supersticiosos a rejeitavam, chamando-a de bruxa. E sendo filha da bruxa, Quruitzia sempre foi ostracizada pelas outras crianças. Os olhos de cores diferentes, naturais nela, eram temidos como "olhos malditos". </t>
         </is>
       </c>
     </row>
@@ -1137,11 +1131,10 @@
 When I visited the village, I found Quruitzia nearly dead on a bed in an abandoned shack on the outskirts. I used alchemy to save her life, which bound our fates together. That’s why she continues to travel with me.</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Após a morte de sua mãe por doença, Quruitzia foi deixada aos cuidados da igreja da vila, onde continuou sendo uma pária. Um dia, ela mesma arrancou um de seus olhos para provar sua inocência.  _x000D_
-_x000D_
-Quando visitei a vila, encontrei Quruitzia à beira da morte, deitada em uma cama dentro de um barraco abandonado nos arredores. Usei alquimia para salvar sua vida, o que uniu nossos destinos. É por isso que ela continua viajando comigo.  </t>
+      <c r="L42" s="20" t="inlineStr">
+        <is>
+          <t>Depois que a mãe morreu de doença, Quruitzia ficou aos cuidados da igreja da vila, onde continuou rejeitada. Um dia, arrancou um dos próprios olhos para provar sua inocência.
+Quando visitei a vila, encontrei Quruitzia quase morta numa cama, numa choupana abandonada nos arredores. Usei a alquimia para salvar a vida dela, e isso atou nossos destinos. É por isso que ela continua a viajar comigo.</t>
         </is>
       </c>
     </row>
@@ -1164,9 +1157,9 @@
           <t>What a story...  To be deemed a witch just because of different eye colors, how absurd!</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Que história... Ser considerada uma bruxa apenas por ter olhos de cores diferentes, que absurdo!  </t>
+      <c r="L43" s="20" t="inlineStr">
+        <is>
+          <t>Que história... Ser chamada de bruxa só pela cor dos olhos, que absurdo!</t>
         </is>
       </c>
     </row>
@@ -1186,11 +1179,10 @@
 I did not share her past to speak of tragedies or the villagers' folly.</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">De fato, eu gostaria de concordar, mas, às vezes, certos 'poderes' realmente se manifestam junto com essas características.  _x000D_
-_x000D_
-Não compartilhei seu passado para falar de tragédias ou da tolice dos aldeões.  </t>
+      <c r="L44" s="20" t="inlineStr">
+        <is>
+          <t>De fato, gostaria de concordar, mas às vezes 'poderes' se manifestam com tais traços.
+Não contei o passado dela para falar de tragédias ou da tolice dos aldeões.</t>
         </is>
       </c>
     </row>
@@ -1200,25 +1192,23 @@
       </c>
       <c r="J45" s="26" t="inlineStr">
         <is>
-          <t>あの日…村を訪れた私が見たのは、命あるもの全てが死に絶えた凄惨な光景だった。それが彼女の「力」によるものかはわからない。だが、ロイテル、そして#pc、君たちには覚えておいてほしい。
+          <t>あの日…村を訪れた私を待っていたは、命あるもの全てが死に絶えた凄惨な静寂だった。それが彼女の「力」によるものかはわからない。だが、ロイテル、そして#pc、君たちには覚えておいてほしい。
 あの子は特別な力の元に生まれ、その力は確実に、彼女を取り巻くものたちの運命に影響を与えるだろう。
 もし君たちが望むなら、私とクルイツゥアは出ていくから、いつでも言ってくれ。</t>
         </is>
       </c>
       <c r="K45" s="25" t="inlineStr">
         <is>
-          <t>That day... what I saw when I visited the village was a horrific scene of death where every living thing had perished. Whether it was her ‘power’ I cannot say. But, Loytel, and you #pc, remember this. 
+          <t>That day... what awaited me in the village I visited was a horrific silence of death　where every living thing had perished. Whether it was her ‘power’ I cannot say. But, Loytel, and you #pc, remember this. 
 She was born under a peculiar power, and that power will undoubtedly affect the fates of those around her.
 If you ever wish us to leave, just say so.</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Aquele dia... o que vi quando visitei a vila foi uma cena horrível de morte, onde toda forma de vida havia perecido. Se foi o 'poder' dela, eu não posso dizer. Mas, Loytel, e você, #pc, lembrem-se disto:  _x000D_
-_x000D_
-Ela nasceu com um poder peculiar, e esse poder, sem dúvida, afetará os destinos daqueles ao seu redor.  _x000D_
-_x000D_
-Se algum dia quiserem que partamos, basta dizer.  </t>
+      <c r="L45" s="20" t="inlineStr">
+        <is>
+          <t>Naquele dia... o que me esperava na vila que visitei era um silêncio de morte horripilante, onde todo ser vivo havia perecido. Se foi o 'poder' dela, não posso dizer. Mas, Loytel, e você #pc, lembrem disto.
+Ela nasceu sob um poder peculiar, e esse poder, sem dúvida, afetará os destinos de quem estiver perto.
+Se algum dia quiserem que partamos, basta dizer.</t>
         </is>
       </c>
       <c r="M45" s="20" t="n"/>
@@ -1242,9 +1232,9 @@
           <t>Oh Kettle...</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Oh, Kettle...  </t>
+      <c r="L46" s="20" t="inlineStr">
+        <is>
+          <t>Ai, Kettle...</t>
         </is>
       </c>
     </row>
@@ -1408,9 +1398,9 @@
           <t>Not a breath of wind, an eerily quiet night. You're there, aren't you, Demitas?</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Nem uma brisa, uma noite assustadoramente silenciosa. Você está aí, não está, Demitas?  </t>
+      <c r="L59" s="20" t="inlineStr">
+        <is>
+          <t>Nem um sopro de vento, uma noite esquisitamente silenciosa. Você está aí, não está, Demitas?</t>
         </is>
       </c>
     </row>
@@ -1433,9 +1423,9 @@
           <t>Heh...I cannot hide from thee.</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Heh... Não posso me esconder de ti.  </t>
+      <c r="L60" s="20" t="inlineStr">
+        <is>
+          <t>Heh...Não há como se esconder de ti.</t>
         </is>
       </c>
     </row>
@@ -1460,11 +1450,10 @@
 Even now, having become such a being, speaking with thee reminds me of when I was human.</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tu és como sempre, Eludin... Pelo menos na aparência.  _x000D_
-_x000D_
-Mesmo agora, tendo me tornado tal ser, falar contigo me faz lembrar de quando eu era humano.  </t>
+      <c r="L61" s="20" t="inlineStr">
+        <is>
+          <t>Tu és como sempre, Eludin... Pelo menos na aparência.
+Mesmo agora, tendo me tornado tal ser, falar contigo me lembra quando era humano.</t>
         </is>
       </c>
     </row>
@@ -1484,11 +1473,10 @@
 You always had a habit of sticking your nose into everything.</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Quando você era humano, hehe... De fato.  _x000D_
-_x000D_
-Você sempre teve o hábito de se intrometer em tudo.  </t>
+      <c r="L62" s="20" t="inlineStr">
+        <is>
+          <t>Quando era humano, hehe... De fato.
+Você sempre teve o hábito de meter o nariz em tudo.</t>
         </is>
       </c>
     </row>
@@ -1508,11 +1496,10 @@
 ...But is that all? You're getting too involved with that girl.</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Vagando entre meus companheiros noite após noite, contando histórias estranhas—isso é bem a sua cara.  _x000D_
-_x000D_
-...Mas é só isso? Você está se envolvendo demais com aquela garota.  </t>
+      <c r="L63" s="20" t="inlineStr">
+        <is>
+          <t>Rondando meus companheiros noite após noite, tecendo contos estranhos: é muito você.
+...Mas é só isso? Você está se envolvendo demais com aquela garota.</t>
         </is>
       </c>
     </row>
@@ -1535,9 +1522,9 @@
           <t>Heh heh heh... Just an old man's concern.</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Heh heh heh... Apenas a preocupação de um velho.  </t>
+      <c r="L64" s="20" t="inlineStr">
+        <is>
+          <t>Heh heh heh... Só a preocupação de um velho.</t>
         </is>
       </c>
     </row>
@@ -1568,11 +1555,10 @@
 The ill-eyed is the stone vessel... And even now, the magic stone sleeping within the dragon child seeks its vessel.</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Aquela garota é perigosa. Tu sabes o que habita em seu olho.  _x000D_
-_x000D_
-A de olhar amaldiçoado é o receptáculo de pedra... E mesmo agora, a pedra mágica que dorme dentro da criança-dragão busca seu receptáculo.  </t>
+      <c r="L66" s="20" t="inlineStr">
+        <is>
+          <t>Aquela garota é perigosa. Sabes o que mora dentro do olho dela.
+A do mau olhado é o recipiente da pedra... E ainda agora, a pedra mágica adormecida dentro do filhote de dragão busca seu recipiente.</t>
         </is>
       </c>
     </row>
@@ -1592,9 +1578,9 @@
           <t>Demitas, I appreciate your concern. But as long as I'm by her side, the magic stone will not awaken.</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Demitas, aprecio sua preocupação. Mas enquanto eu estiver ao lado dela, a pedra mágica não despertará.  </t>
+      <c r="L67" s="20" t="inlineStr">
+        <is>
+          <t>Demitas, agradeço sua preocupação. Mas enquanto eu estiver ao lado dela, a pedra mágica não despertará.</t>
         </is>
       </c>
     </row>
@@ -1635,9 +1621,9 @@
           <t>I see, if the "First Alchemist" says so, it must be true.</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Entendo, se o 'Primeiro Alquimista' diz isso, então deve ser verdade.  </t>
+      <c r="L70" s="20" t="inlineStr">
+        <is>
+          <t>Entendo, se o "Primeiro Alquimista" o afirma, deve ser verdade.</t>
         </is>
       </c>
     </row>
@@ -1666,7 +1652,7 @@
           <t>Heh heh heh...</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr">
+      <c r="L72" s="20" t="inlineStr">
         <is>
           <t>Heh heh heh...</t>
         </is>
@@ -1707,9 +1693,9 @@
           <t>...Even so, Eludin, fate will find Quruitzia and Corgon.</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">...Mesmo assim, Eludin, o destino encontrará Quruitzia e Corgon.  </t>
+      <c r="L74" s="20" t="inlineStr">
+        <is>
+          <t>...Ainda assim, Eludin, o destino encontrará Quruitzia e Corgon.</t>
         </is>
       </c>
     </row>
@@ -1736,9 +1722,9 @@
           <t>The rumor of a dragon child living among humans will soon be known by all. Of course, none would dare to harm the dragon... Save one.</t>
         </is>
       </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>O rumor de uma criança-dragão vivendo entre humanos em breve será conhecido por todos. É claro que ninguém ousaria ferir o dragão... Exceto um.</t>
+      <c r="L76" s="20" t="inlineStr">
+        <is>
+          <t>O rumor de um filhote de dragão vivendo entre humanos logo será sabido por todos. E claro, ninguém ousaria machucar o dragão... Salvo um.</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1742,7 @@
           <t>...</t>
         </is>
       </c>
-      <c r="L77" t="inlineStr">
+      <c r="L77" s="20" t="inlineStr">
         <is>
           <t>...</t>
         </is>
@@ -1789,13 +1775,11 @@
 That one will hunt down Quruitzia and Corgon.</t>
         </is>
       </c>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Há alguém que conhece a lenda de que a pedra mágica foi entregue ao Dragão de Aço na época do Rei Zashim, alguém que tem buscado desesperadamente a pedra mágica perdida desde a morte do dragão.  _x000D_
-_x000D_
-Esse alguém ouvirá sobre a criança-dragão e compreenderá seu significado.  _x000D_
-_x000D_
-Esse alguém caçará Quruitzia e Corgon.  </t>
+      <c r="L79" s="20" t="inlineStr">
+        <is>
+          <t>Há um que conhece a lenda de que a pedra mágica foi entregue ao Dragão de Aço no tempo do rei Zashim, um que busca desesperadamente a pedra mágica perdida desde a morte do dragão.
+Esse um ouvirá do filhote de dragão e entenderá seu significado.
+Esse um caçará Quruitzia e Corgon.</t>
         </is>
       </c>
     </row>
@@ -1813,9 +1797,9 @@
           <t>...Issizzle.</t>
         </is>
       </c>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">...Issizzle.  </t>
+      <c r="L80" s="20" t="inlineStr">
+        <is>
+          <t>...Issizzle.</t>
         </is>
       </c>
     </row>
@@ -1840,11 +1824,10 @@
 Once a mighty sorcerer who didst earn great renown, now a foul creature ensnared by the magic stone, fallen into darkness... And thy pitiable disciple, whom thou couldst neither slay nor save.</t>
         </is>
       </c>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sim, 'Issizzle', a abominação sombria.  _x000D_
-_x000D_
-Outrora um grande feiticeiro de renome, agora uma criatura desprezível enredada pela pedra mágica, caída na escuridão... E teu discípulo miserável, a quem não pudeste nem matar nem salvar.  </t>
+      <c r="L81" s="20" t="inlineStr">
+        <is>
+          <t>Sim, "Issizzle", a abominação das trevas.
+Outrora um poderoso feiticeiro que granjeou grande renome, agora uma criatura imunda enlaçada pela pedra mágica, caída nas trevas... E o teu discípulo lastimável, que não pudeste nem matar nem salvar.</t>
         </is>
       </c>
     </row>
@@ -1862,9 +1845,9 @@
           <t>...</t>
         </is>
       </c>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">...  </t>
+      <c r="L82" s="20" t="inlineStr">
+        <is>
+          <t>...</t>
         </is>
       </c>
     </row>
@@ -1889,11 +1872,10 @@
 Eventually, she will either become enslaved by the magic stone, be used by him, or be killed...</t>
         </is>
       </c>
-      <c r="L83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">O que farás com essa garota?  _x000D_
-_x000D_
-Eventualmente, ela será escravizada pela pedra mágica, usada por ele ou morta...  </t>
+      <c r="L83" s="20" t="inlineStr">
+        <is>
+          <t>O que farás com aquela garota?
+Cedo ou tarde, ela será escravizada pela pedra mágica, será usada por ele, ou será morta...</t>
         </is>
       </c>
     </row>
@@ -1918,9 +1900,10 @@
 There is no salvation for that girl. Thou art about to repeat the same mistake. And thy leniency will once again bring calamity upon this world.</t>
         </is>
       </c>
-      <c r="L84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Não desvie os olhos da verdade, 'Kettle'.  </t>
+      <c r="L84" s="20" t="inlineStr">
+        <is>
+          <t>Não desvies teus olhos da verdade, "Kettle."
+Não há salvação para aquela garota. Estás prestes a repetir o mesmo erro. E tua brandura trará de novo a calamidade sobre este mundo.</t>
         </is>
       </c>
     </row>
@@ -2098,9 +2081,9 @@
           <t>Everyone, may I have a moment?</t>
         </is>
       </c>
-      <c r="L99" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Todos, posso pedir um momento?  </t>
+      <c r="L99" s="20" t="inlineStr">
+        <is>
+          <t>Todos, posso ter a atenção de vocês um momento?</t>
         </is>
       </c>
     </row>
@@ -2123,9 +2106,9 @@
           <t>Mokyu?</t>
         </is>
       </c>
-      <c r="L100" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mokyu?  </t>
+      <c r="L100" s="20" t="inlineStr">
+        <is>
+          <t>Mokyu?</t>
         </is>
       </c>
     </row>
@@ -2148,9 +2131,9 @@
           <t>What's the matter, Kettle? At this hour?</t>
         </is>
       </c>
-      <c r="L101" t="inlineStr">
-        <is>
-          <t xml:space="preserve">O que houve, Kettle? A essa hora?  </t>
+      <c r="L101" s="20" t="inlineStr">
+        <is>
+          <t>Que foi, Kettle? A esta hora?</t>
         </is>
       </c>
     </row>
@@ -2175,11 +2158,10 @@
 I want you all to know about it. A man who was once my apprentice, and the power smoldering within Quruitzia's eye...</t>
         </is>
       </c>
-      <c r="L102" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Há um perigo se aproximando de nós.  _x000D_
-_x000D_
-Quero que todos saibam disso. Um homem que um dia foi meu aprendiz, e o poder que arde dentro do olho de Quruitzia...  </t>
+      <c r="L102" s="20" t="inlineStr">
+        <is>
+          <t>Há um perigo nos aproximando.
+Quero que todos saibam. Um homem que um dia foi meu discípulo, e o poder que fumega dentro do olho de Quruitzia...</t>
         </is>
       </c>
     </row>
@@ -2249,11 +2231,10 @@
 The ancient witch’s blood that runs through Quruitzia, and then there’s the Magic Stone within Corgon’s small body?</t>
         </is>
       </c>
-      <c r="L107" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Entendo... Minha cabeça parece que vai girar.  _x000D_
-_x000D_
-O sangue da antiga bruxa que corre em Quruitzia, e então há a Pedra Mágica dentro do pequeno corpo de Corgon?  </t>
+      <c r="L107" s="20" t="inlineStr">
+        <is>
+          <t>Entendo... Sinto a cabeça girando.
+O sangue de bruxa antiga que corre em Quruitzia, e ainda por cima a Pedra Mágica dentro do corpinho do Corgon?</t>
         </is>
       </c>
     </row>
@@ -2278,9 +2259,9 @@
           <t>If what you’re saying is true, Kettle, and Issizzle is coming for the Magic Stone... then we must prepare immediately. We have to protect Quruitzia and Corgon.</t>
         </is>
       </c>
-      <c r="L108" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Se o que você está dizendo for verdade, Kettle, e Issizzle estiver vindo atrás da Pedra Mágica... então devemos nos preparar imediatamente. Precisamos proteger Quruitzia e Corgon.  </t>
+      <c r="L108" s="20" t="inlineStr">
+        <is>
+          <t>Se o que você diz é verdade, Kettle, e Issizzle vem atrás da Pedra Mágica... então temos de nos preparar já. Temos de proteger Quruitzia e Corgon.</t>
         </is>
       </c>
     </row>
@@ -2311,9 +2292,9 @@
           <t>Heh heh heh...</t>
         </is>
       </c>
-      <c r="L110" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Heh heh heh...  </t>
+      <c r="L110" s="20" t="inlineStr">
+        <is>
+          <t>Heh heh heh...</t>
         </is>
       </c>
     </row>
@@ -2338,9 +2319,9 @@
           <t>And there you are again. What’s so amusing?</t>
         </is>
       </c>
-      <c r="L111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Aí está você de novo. O que acha tão engraçado?  </t>
+      <c r="L111" s="20" t="inlineStr">
+        <is>
+          <t>E lá está você de novo. O que é tão engraçado?</t>
         </is>
       </c>
     </row>
@@ -2365,11 +2346,10 @@
 The world itself shows signs of its end, due to their very existence.</t>
         </is>
       </c>
-      <c r="L112" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A segurança da garota e da criança-dragão não importa.  _x000D_
-_x000D_
-O próprio mundo mostra sinais de seu fim, devido à mera existência deles.  </t>
+      <c r="L112" s="20" t="inlineStr">
+        <is>
+          <t>A segurança da garota e do filhote de dragão não importa.
+O próprio mundo mostra sinais do seu fim, por causa da existência deles.</t>
         </is>
       </c>
     </row>
@@ -2392,9 +2372,9 @@
           <t>What do you mean, Demitas?</t>
         </is>
       </c>
-      <c r="L113" t="inlineStr">
-        <is>
-          <t xml:space="preserve">O que quer dizer, Demitas?  </t>
+      <c r="L113" s="20" t="inlineStr">
+        <is>
+          <t>Como assim, Demitas?</t>
         </is>
       </c>
     </row>
@@ -2417,9 +2397,9 @@
           <t>Their beings... the Old Ones bring naught but calamity and stagnation unto the world. Their might is a source of distortion, and their brilliance doth consume all that surrounds them in flame.</t>
         </is>
       </c>
-      <c r="L114" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Seres como eles... Os Antigos não trazem nada além de calamidade e estagnação ao mundo. Seu poder é uma fonte de distorção, e seu brilho consome tudo ao redor em chamas.  </t>
+      <c r="L114" s="20" t="inlineStr">
+        <is>
+          <t>Os seres deles... os Antigos só trazem calamidade e estagnação ao mundo. O poder deles é fonte de distorção, e o brilho deles consome em chamas tudo o que os cerca.</t>
         </is>
       </c>
     </row>
@@ -2444,11 +2424,10 @@
 It is for this reason that the gods did cease their meddling with mankind and departed from the earth. The Old Ones... the children wrought by the gods should follow their example as well.</t>
         </is>
       </c>
-      <c r="L115" t="inlineStr">
-        <is>
-          <t xml:space="preserve">O significado que nos esforçamos para construir é pisoteado por suas leis, como se fosse apenas poeira. Impotentes e trêmulos, tornamo-nos meros fantoches, condenados a assistir ao destino se desenrolar. Queiram ou não, é sempre assim. Que progresso poderia jamais enraizar-se em um mundo como este?  _x000D_
-_x000D_
-É por essa razão que os deuses cessaram sua interferência na humanidade e partiram da terra. Os Antigos... os filhos criados pelos deuses deveriam seguir seu exemplo também.  </t>
+      <c r="L115" s="20" t="inlineStr">
+        <is>
+          <t>O sentido que nos esforçamos por construir é pisado por suas leis como se fosse poeira. Sem poder e trêmulos, viramos meros fantoches, condenados a assistir o destino se desdobrar. Queiram esses seres ou não, tanto faz. Que progresso poderia criar raiz num mundo assim?
+É por isso que os deuses deixaram de se intrometer com a humanidade e partiram da terra. Os Antigos... os filhos forjados pelos deuses deveriam seguir o mesmo exemplo.</t>
         </is>
       </c>
     </row>
@@ -2471,9 +2450,9 @@
           <t>...Eh?</t>
         </is>
       </c>
-      <c r="L116" t="inlineStr">
-        <is>
-          <t xml:space="preserve">...Hã?  </t>
+      <c r="L116" s="20" t="inlineStr">
+        <is>
+          <t>...Hã?</t>
         </is>
       </c>
     </row>
@@ -2498,11 +2477,10 @@
 Hast thou forgotten the calamity thy mercy hath wrought, Kettle? Thou shouldst have slain Issizle. And thou shouldst slay this girl and the dragon child as well.</t>
         </is>
       </c>
-      <c r="L117" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Na verdade, o mundo não precisa de Issizzle, nem de uma criança-dragão ou de uma bruxa. Melhor que desapareçam e sejam esquecidos.  _x000D_
-_x000D_
-Acaso esqueceste a calamidade que tua misericórdia causou, Kettle? Devias ter matado Issizzle. E devias matar essa garota e a criança-dragão também.  </t>
+      <c r="L117" s="20" t="inlineStr">
+        <is>
+          <t>Em verdade, o mundo não precisa de Issizzle, nem de um filhote de dragão e uma bruxa. Melhor que partam e sejam esquecidos.
+Esqueceste a calamidade que tua piedade forjou, Kettle? Deverias ter morto Issizzle. E deverias matar esta garota e o filhote de dragão também.</t>
         </is>
       </c>
     </row>
@@ -2525,7 +2503,7 @@
           <t>...</t>
         </is>
       </c>
-      <c r="L118" t="inlineStr">
+      <c r="L118" s="20" t="inlineStr">
         <is>
           <t>...</t>
         </is>
@@ -2560,11 +2538,10 @@
 Who do you think you are to say such things about these children’s lives?</t>
         </is>
       </c>
-      <c r="L120" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ei, espere um momento. Não posso simplesmente deixar isso passar.  _x000D_
-_x000D_
-Quem você pensa que é para falar assim sobre a vida dessas crianças?  </t>
+      <c r="L120" s="20" t="inlineStr">
+        <is>
+          <t>Ora, espera um momento. Não posso deixar isso passar.
+Quem você pensa que é para falar essas coisas das vidas dessas crianças?</t>
         </is>
       </c>
     </row>
@@ -2584,12 +2561,12 @@
       </c>
       <c r="K121" s="28" t="inlineStr">
         <is>
-          <t>Quruitzia is a dangerous being. Thou knowest it well. The girl's Ill-Eye brought death to an entire village. And that power hath not even 'awakened' yet.</t>
-        </is>
-      </c>
-      <c r="L121" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Quruitzia é um ser perigoso. Tu bem o sabes. O Olho Amaldiçoado da garota trouxe morte a uma vila inteira. E esse poder ainda nem 'despertou'.  </t>
+          <t>Quruitzia is a dangerous being. Thou knowest it well. The girl's Ill Eye brought death to an entire village. And that power hath not even 'awakened' yet.</t>
+        </is>
+      </c>
+      <c r="L121" s="20" t="inlineStr">
+        <is>
+          <t>Quruitzia é um ser perigoso. Bem o sabes. O Olho Mau da garota trouxe morte a uma vila inteira. E esse poder nem 'despertou' ainda.</t>
         </is>
       </c>
     </row>
@@ -2614,11 +2591,10 @@
 She didn’t even understand her own power. Blaming her for that is just too cruel.</t>
         </is>
       </c>
-      <c r="L122" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mas o que o desencadeou? Não foram os aldeões supersticiosos que levaram Quruitzia ao limite?  _x000D_
-_x000D_
-Ela nem sequer compreendia seu próprio poder. Culpá-la por isso é simplesmente cruel demais.  </t>
+      <c r="L122" s="20" t="inlineStr">
+        <is>
+          <t>Mas o que o disparou? Não foram os aldeões supersticiosos que empurraram Quruitzia para o limite?
+Ela nem entendia o próprio poder. Culpar ela por isso é cruel demais.</t>
         </is>
       </c>
     </row>
@@ -2641,9 +2617,9 @@
           <t>Then, for the sake of mercy toward this girl, dost thou not mind if this world perisheth?</t>
         </is>
       </c>
-      <c r="L123" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Então, por misericórdia para com essa garota, não te importas se este mundo perecer?  </t>
+      <c r="L123" s="20" t="inlineStr">
+        <is>
+          <t>Então, pela piedade para com esta garota, não te importa se este mundo perecer?</t>
         </is>
       </c>
     </row>
@@ -2680,9 +2656,9 @@
           <t>W-well, that's...</t>
         </is>
       </c>
-      <c r="L125" t="inlineStr">
-        <is>
-          <t>E-eu... isso é…</t>
+      <c r="L125" s="20" t="inlineStr">
+        <is>
+          <t>B-bem, isso é...</t>
         </is>
       </c>
     </row>
@@ -2733,9 +2709,9 @@
           <t>...I don't mind. If this world denies Quruitzia's existence based on such reasoning, then it might as well perish.</t>
         </is>
       </c>
-      <c r="L129" t="inlineStr">
-        <is>
-          <t xml:space="preserve">...Eu não me importo. Se este mundo nega a existência de Quruitzia com base em tais argumentos, então que pereça.  </t>
+      <c r="L129" s="20" t="inlineStr">
+        <is>
+          <t>...Não me importa. Se este mundo nega a existência de Quruitzia com um raciocínio desses, então que pereça.</t>
         </is>
       </c>
     </row>
@@ -2758,9 +2734,9 @@
           <t>Mokyu!</t>
         </is>
       </c>
-      <c r="L130" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mokyu!  </t>
+      <c r="L130" s="20" t="inlineStr">
+        <is>
+          <t>Mokyu!</t>
         </is>
       </c>
     </row>
@@ -2783,9 +2759,9 @@
           <t>La...Lady Farris, isn't that going a bit too far...</t>
         </is>
       </c>
-      <c r="L131" t="inlineStr">
-        <is>
-          <t xml:space="preserve">La... Lady Farris, isso não é um pouco exagerado...?  </t>
+      <c r="L131" s="20" t="inlineStr">
+        <is>
+          <t>La...Lady Farris, isso não está indo longe demais...</t>
         </is>
       </c>
     </row>
@@ -2810,11 +2786,10 @@
 ...It's only natural, isn't it, Lord Loytel? </t>
         </is>
       </c>
-      <c r="L132" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Não, Lorde Loytel. Quruitzia é uma companheira querida para nós. Farei o que for preciso para protegê-la, mesmo que isso signifique desafiar as leis deste mundo.  _x000D_
-_x000D_
-...É apenas natural, não é, Lorde Loytel?  </t>
+      <c r="L132" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Não, Lorde Loytel. Quruitzia é uma companheira querida. Farei o que for preciso para protegê-la, ainda que seja desafiar as leis deste mundo.
+...É o natural, não é, Lorde Loytel? </t>
         </is>
       </c>
     </row>
@@ -2837,9 +2812,9 @@
           <t>O...</t>
         </is>
       </c>
-      <c r="L133" t="inlineStr">
-        <is>
-          <t xml:space="preserve">O...  </t>
+      <c r="L133" s="20" t="inlineStr">
+        <is>
+          <t>O...</t>
         </is>
       </c>
     </row>
@@ -2864,11 +2839,10 @@
 You have opened my eyes once again, Lady Farris.</t>
         </is>
       </c>
-      <c r="L134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">É claro!  _x000D_
-_x000D_
-Você abriu meus olhos mais uma vez, Lady Farris.  </t>
+      <c r="L134" s="20" t="inlineStr">
+        <is>
+          <t>Claro!
+Você abriu meus olhos mais uma vez, Lady Farris.</t>
         </is>
       </c>
     </row>
@@ -2895,13 +2869,11 @@
 That's all there is to it. Naturally.</t>
         </is>
       </c>
-      <c r="L135" t="inlineStr">
-        <is>
-          <t xml:space="preserve">O destino do mundo ou qualquer outra coisa, isso não me interessa.  _x000D_
-_x000D_
-O destino de Quruitzia pertence a ela, e não deixaremos que ninguém o dite—nem Issizzle, nem ninguém.  _x000D_
-_x000D_
-Isso é tudo. Naturalmente.  </t>
+      <c r="L135" s="20" t="inlineStr">
+        <is>
+          <t>O destino do mundo ou o que for, não é comigo.
+O destino de Quruitzia é dela para decidir, e não deixaremos mais ninguém ditar: nem Issizzle, nem ninguém.
+É só isso que importa. Naturalmente.</t>
         </is>
       </c>
     </row>
@@ -2924,9 +2896,9 @@
           <t>Mokyu!</t>
         </is>
       </c>
-      <c r="L136" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mokyu!  </t>
+      <c r="L136" s="20" t="inlineStr">
+        <is>
+          <t>Mokyu!</t>
         </is>
       </c>
     </row>
@@ -2951,11 +2923,10 @@
 These two spend all day cuddling and calling each other “Ma...maa...” and “Corgon♪,” you know?</t>
         </is>
       </c>
-      <c r="L137" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Além disso, Demitas, não compare Quruitzia com aberrações perigosas como Issizzle quando falar sobre os 'Antigos'.  _x000D_
-_x000D_
-Esses dois passam o dia inteiro se abraçando e chamando um ao outro de ‘Ma...maa...’ e ‘Corgon♪’, sabia?  </t>
+      <c r="L137" s="20" t="inlineStr">
+        <is>
+          <t>Além disso, Demitas, não coloque Quruitzia no mesmo balaio de aberrações perigosas como Issizzle quando fala dos 'Antigos'.
+Esses dois passam o dia se aninhando e se chamando de "Mã...maa..." e "Corgon♪", sabia?</t>
         </is>
       </c>
     </row>
@@ -2978,9 +2949,9 @@
           <t>Farris... Loytel...</t>
         </is>
       </c>
-      <c r="L138" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Farris... Loytel...  </t>
+      <c r="L138" s="20" t="inlineStr">
+        <is>
+          <t>Farris... Loytel...</t>
         </is>
       </c>
     </row>
@@ -3003,9 +2974,9 @@
           <t>...</t>
         </is>
       </c>
-      <c r="L139" t="inlineStr">
-        <is>
-          <t xml:space="preserve">...  </t>
+      <c r="L139" s="20" t="inlineStr">
+        <is>
+          <t>...</t>
         </is>
       </c>
     </row>
@@ -3030,11 +3001,10 @@
 Ye know not. Ye cannot save, nor can ye slay, and therein lies a suffering unbeknownst to thee. Thy softness shall bring naught but further sorrow upon this girl!</t>
         </is>
       </c>
-      <c r="L140" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tolos, levados pela emoção, ignorando a razão... E assim, os mesmos erros se repetem.  _x000D_
-_x000D_
-Vós não sabeis. Não podeis salvar, nem podeis matar, e nisso reside um sofrimento que desconheceis. Vossa suavidade não trará nada além de mais dor para essa garota!  </t>
+      <c r="L140" s="20" t="inlineStr">
+        <is>
+          <t>Tolos, levados pela emoção, surdos à razão... Assim, os mesmos erros se repetem.
+Não sabeis. Não podeis salvar, nem podeis matar, e aí jaz um sofrimento que desconheceis. Vossa brandura só trará mais tristeza sobre esta garota!</t>
         </is>
       </c>
     </row>
@@ -3052,9 +3022,9 @@
           <t>Demitas... It's her...isn't it? ...You still think of Telessia.</t>
         </is>
       </c>
-      <c r="L141" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Demitas... É por causa dela, não é? ...Você ainda pensa em Telessia.  </t>
+      <c r="L141" s="20" t="inlineStr">
+        <is>
+          <t>Demitas... É ela... não é? ...Você ainda pensa em Telessia.</t>
         </is>
       </c>
     </row>
@@ -3077,9 +3047,9 @@
           <t>Telessia...? She... Heh, I see... Heh heh heh... So that's how it is.</t>
         </is>
       </c>
-      <c r="L142" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Telessia...? Ela... Heh, entendo... Heh heh heh... Então é assim.  </t>
+      <c r="L142" s="20" t="inlineStr">
+        <is>
+          <t>Telessia...? Ela... Heh, entendi... Heh heh heh... Então é assim.</t>
         </is>
       </c>
     </row>
@@ -3102,9 +3072,9 @@
           <t>Heh heh heh... Her resemblance... and I, of all people...</t>
         </is>
       </c>
-      <c r="L143" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Heh heh heh... A semelhança... e eu, logo eu...  </t>
+      <c r="L143" s="20" t="inlineStr">
+        <is>
+          <t>Heh heh heh... A semelhança... e eu, de todas as pessoas...</t>
         </is>
       </c>
     </row>
@@ -3129,11 +3099,10 @@
 For now, let's all work together and think of a way to drive Issizzle away.</t>
         </is>
       </c>
-      <c r="L144" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bem, acho que ainda não nos conhecemos tão bem. Mas isso é algo que o tempo pode resolver.  _x000D_
-_x000D_
-Por agora, vamos trabalhar juntos e pensar em uma forma de afastar Issizzle.  </t>
+      <c r="L144" s="20" t="inlineStr">
+        <is>
+          <t>Bom, acho que ainda não nos conhecemos bem. Mas isso o tempo resolve.
+Por ora, vamos trabalhar juntos e pensar num jeito de afastar Issizzle.</t>
         </is>
       </c>
     </row>
@@ -3158,11 +3127,10 @@
 ...But perhaps we should leave it at that for today. Dawn is nearly upon us.</t>
         </is>
       </c>
-      <c r="L145" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Concordo, Loytel. Eu mesmo tenho algumas ideias sobre isso.  _x000D_
-_x000D_
-...Mas talvez devêssemos encerrar por hoje. O amanhecer está próximo.  </t>
+      <c r="L145" s="20" t="inlineStr">
+        <is>
+          <t>Concordo, Loytel. Eu mesma tenho algumas ideias.
+...Mas talvez paremos por hoje. A aurora está quase chegando.</t>
         </is>
       </c>
     </row>
@@ -3187,11 +3155,10 @@
 #pc, you’ve been listening, haven’t you? It looks like things are going to get pretty busy from now on.</t>
         </is>
       </c>
-      <c r="L146" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Heh, pensar que levamos a noite inteira para chegar a uma conclusão tão óbvia.  _x000D_
-_x000D_
-#pc, você estava ouvindo, não estava? Parece que as coisas vão ficar bem agitadas de agora em diante.  </t>
+      <c r="L146" s="20" t="inlineStr">
+        <is>
+          <t>Heh, e olha que levamos a noite toda para chegar a uma conclusão óbvia.
+#pc, você estava ouvindo, não estava? As coisas vão ficar bem corridas daqui para frente.</t>
         </is>
       </c>
     </row>
@@ -3530,17 +3497,17 @@
       </c>
       <c r="J159" s="33" t="inlineStr">
         <is>
-          <t>- 古城 -</t>
+          <t>- 古塔 -</t>
         </is>
       </c>
       <c r="K159" s="33" t="inlineStr">
         <is>
-          <t>- Old Castle -</t>
-        </is>
-      </c>
-      <c r="L159" t="inlineStr">
-        <is>
-          <t>- Castelo Antigo -</t>
+          <t>- Old Tower -</t>
+        </is>
+      </c>
+      <c r="L159" s="20" t="inlineStr">
+        <is>
+          <t>- Torre Antiga -</t>
         </is>
       </c>
       <c r="M159" s="20" t="n"/>
@@ -3812,7 +3779,7 @@
           <t>...Sorin, is that you? How many years have passed since we last met.</t>
         </is>
       </c>
-      <c r="L161" t="inlineStr">
+      <c r="L161" s="20" t="inlineStr">
         <is>
           <t>...Sorin, é você? Quantos anos se passaram desde nosso último encontro.</t>
         </is>
@@ -3837,7 +3804,7 @@
           <t>Do you still remember me?</t>
         </is>
       </c>
-      <c r="L162" t="inlineStr">
+      <c r="L162" s="20" t="inlineStr">
         <is>
           <t>Ainda se lembra de mim?</t>
         </is>
@@ -3862,9 +3829,9 @@
           <t>(ancient words, unintelligible)</t>
         </is>
       </c>
-      <c r="L163" t="inlineStr">
-        <is>
-          <t>(palavras ancestrais, ininteligíveis)</t>
+      <c r="L163" s="20" t="inlineStr">
+        <is>
+          <t>(palavras antigas, ininteligíveis)</t>
         </is>
       </c>
     </row>
@@ -3887,7 +3854,7 @@
           <t>...</t>
         </is>
       </c>
-      <c r="L164" t="inlineStr">
+      <c r="L164" s="20" t="inlineStr">
         <is>
           <t>...</t>
         </is>
@@ -3912,9 +3879,9 @@
           <t>(ancient words, unintelligible)</t>
         </is>
       </c>
-      <c r="L165" t="inlineStr">
-        <is>
-          <t>(palavras ancestrais, ininteligíveis)</t>
+      <c r="L165" s="20" t="inlineStr">
+        <is>
+          <t>(palavras antigas, ininteligíveis)</t>
         </is>
       </c>
     </row>
@@ -3937,7 +3904,7 @@
           <t>I'm surprised. Then you still...</t>
         </is>
       </c>
-      <c r="L166" t="inlineStr">
+      <c r="L166" s="20" t="inlineStr">
         <is>
           <t>Estou surpreso. Então você ainda...</t>
         </is>
@@ -3962,9 +3929,9 @@
           <t>(ancient words, unintelligible)</t>
         </is>
       </c>
-      <c r="L167" t="inlineStr">
-        <is>
-          <t>(palavras ancestrais, ininteligíveis)</t>
+      <c r="L167" s="20" t="inlineStr">
+        <is>
+          <t>(palavras antigas, ininteligíveis)</t>
         </is>
       </c>
     </row>
@@ -3987,9 +3954,9 @@
           <t>You waited? ...For me?</t>
         </is>
       </c>
-      <c r="L168" t="inlineStr">
-        <is>
-          <t>Você esperou? ...Por mim?</t>
+      <c r="L168" s="20" t="inlineStr">
+        <is>
+          <t>Esperou? ...Por mim?</t>
         </is>
       </c>
     </row>
@@ -4012,7 +3979,7 @@
           <t>...</t>
         </is>
       </c>
-      <c r="L169" t="inlineStr">
+      <c r="L169" s="20" t="inlineStr">
         <is>
           <t>...</t>
         </is>
@@ -4070,7 +4037,7 @@
           <t>...</t>
         </is>
       </c>
-      <c r="L173" t="inlineStr">
+      <c r="L173" s="20" t="inlineStr">
         <is>
           <t>...</t>
         </is>
@@ -4097,9 +4064,9 @@
           <t>Hmph, close enough. It has been a long time since I took this shape.</t>
         </is>
       </c>
-      <c r="L174" t="inlineStr">
-        <is>
-          <t>Hmph, próximo o suficiente. Faz muito tempo desde que assumi esta forma.</t>
+      <c r="L174" s="20" t="inlineStr">
+        <is>
+          <t>Hmph, quase. Faz muito tempo que assumi esta forma.</t>
         </is>
       </c>
     </row>
@@ -4124,9 +4091,9 @@
           <t>Well then, does this make it easier to speak, Master?</t>
         </is>
       </c>
-      <c r="L175" t="inlineStr">
-        <is>
-          <t>Bem, isso facilita a conversa, Mestre?</t>
+      <c r="L175" s="20" t="inlineStr">
+        <is>
+          <t>Pois bem, isso facilita conversar, Mestre?</t>
         </is>
       </c>
     </row>
@@ -4151,9 +4118,9 @@
           <t>I'm relieved, Sorin—relieved that you still remember who you once were.</t>
         </is>
       </c>
-      <c r="L176" t="inlineStr">
-        <is>
-          <t>Estou aliviado, Sorin... aliviado por você ainda se lembrar de quem já foi.</t>
+      <c r="L176" s="20" t="inlineStr">
+        <is>
+          <t>Fico aliviado, Sorin: aliviado que você ainda se lembra de quem um dia foi.</t>
         </is>
       </c>
     </row>
@@ -4177,13 +4144,13 @@
       <c r="K177" s="28" t="inlineStr">
         <is>
           <t>How ironic. Whether I remember this old face or not, I never possessed the humanity you hoped for in the first place.
-...No matter. I’ve no wish to sour a reunion two centuries in the making. Let us talk here, as we once did in this dusky room... of the very crystal we call the Magic Stone.”</t>
-        </is>
-      </c>
-      <c r="L177" t="inlineStr">
-        <is>
-          <t>Que irônico. Se me lembro ou não deste velho rosto, nunca tive a humanidade que você esperava desde o início.
-...Não importa. Não desejo estragar um reencontro após dois séculos. Vamos conversar aqui, como fazíamos nesta sala crepuscular... sobre o próprio cristal que chamamos de Pedra Mágica.”</t>
+...No matter. I’ve no wish to sour a reunion two centuries in the making. Let us talk here, as we once did in this dusky room... of the very crystal we call the "Magic Stone.”</t>
+        </is>
+      </c>
+      <c r="L177" s="20" t="inlineStr">
+        <is>
+          <t>Que ironia. Quer você se lembre desta velha cara ou não, eu nunca tive a humanidade que você esperava, para começar.
+...Tanto faz. Não tenho vontade de azedar um reencontro de dois séculos. Conversemos aqui, como fazíamos nesta sala crepuscular... sobre o próprio cristal a que chamamos "Pedra Mágica".</t>
         </is>
       </c>
     </row>
@@ -4208,9 +4175,9 @@
           <t>It seems you foresaw that I would come—and why.</t>
         </is>
       </c>
-      <c r="L178" t="inlineStr">
-        <is>
-          <t>Parece que você previu que eu viria... e por quê.</t>
+      <c r="L178" s="20" t="inlineStr">
+        <is>
+          <t>Parece que previu que eu viria, e por quê.</t>
         </is>
       </c>
     </row>
@@ -4237,10 +4204,10 @@
 ...Until quite recently, when you found Corgon’s last offspring.</t>
         </is>
       </c>
-      <c r="L179" t="inlineStr">
-        <is>
-          <t>...O Dragão de Aço, “Corgon”. Certa vez, ele recebeu uma Pedra Mágica do Rei de Palmia. O matador de dragões “Thorran” abateu aquela fera há cerca de vinte anos. No entanto, o tolo voltou sem a Pedra, e seu paradeiro mergulhou na escuridão.
-...Até recentemente, quando você encontrou o último descendente de Corgon.</t>
+      <c r="L179" s="20" t="inlineStr">
+        <is>
+          <t>...O Dragão de Aço, "Corgon". Outrora recebeu uma Pedra Mágica do Rei de Palmia. O matador de dragões "Thorran" abateu a besta há uns vinte anos. Mas o tolo voltou sem a Pedra, e o paradeiro dela afundou na escuridão.
+...Até que, há bem pouco tempo, você encontrou o último descendente de Corgon.</t>
         </is>
       </c>
     </row>
@@ -4258,19 +4225,19 @@
       <c r="J180" s="26" t="inlineStr">
         <is>
           <t>竜の子の噂を耳にしたその日のうちには、僕は彼の居場所を見つけていました。容易いことです。僕はすぐにでも竜の子を殺し、魔石を奪うこともできた。しかし、竜の子の傍らに、あなたの姿を見とめたのです。
-そこで、この城であなたを待つことにしました。あなたなら、必ずやって来ると、わかっていたのでね。</t>
+そこで、この塔であなたを待つことにしました。あなたなら、必ずやって来ると、わかっていたのでね。</t>
         </is>
       </c>
       <c r="K180" s="28" t="inlineStr">
         <is>
           <t>The very day the rumor reached me, I found the whelp’s refuge. It would have been easy to kill him and take the Stone at once. But I saw you at the child’s side.
-So I chose to wait for you in this castle. I knew you would come.</t>
-        </is>
-      </c>
-      <c r="L180" t="inlineStr">
-        <is>
-          <t>No mesmo dia em que o rumor chegou até mim, encontrei o refúgio do filhote. Teria sido fácil matá-lo e tomar a Pedra de uma vez. Mas vi você ao lado da criança.
-Então, escolhi esperar por você neste castelo. Eu sabia que viria.</t>
+So I chose to wait for you in this tower. I knew you would come.</t>
+        </is>
+      </c>
+      <c r="L180" s="20" t="inlineStr">
+        <is>
+          <t>No mesmo dia em que o rumor me alcançou, encontrei o refúgio do filhote. Teria sido fácil matá-lo e tomar a Pedra na hora. Mas vi você ao lado da criança.
+Então escolhi esperá-lo nesta torre. Sabia que viria.</t>
         </is>
       </c>
     </row>
@@ -4297,10 +4264,10 @@
 You once agreed to my plan—granted, that was centuries ago. What changed your heart in the meantime? For you came to me without the whelp in tow, which means you have no intention of aiding me further.</t>
         </is>
       </c>
-      <c r="L181" t="inlineStr">
-        <is>
-          <t>Agora, diga-me, Mestre—o que pretende fazer com aquele filhote de dragão... e com a Pedra dentro do corpo do dragão?
-Você já concordou com meu plano—embora isso tenha sido séculos atrás. O que mudou seu coração nesse meio-tempo? Pois veio até mim sem o filhote, o que significa que não tem intenção de me ajudar mais.</t>
+      <c r="L181" s="20" t="inlineStr">
+        <is>
+          <t>Agora, diga-me, Mestre: o que pretende fazer com aquele filhote de dragão... e com a Pedra dentro do corpo do dragão?
+O senhor um dia concordou com meu plano: certo, isso foi séculos atrás. O que mudou seu coração nesse meio-tempo? Você veio até mim sem trazer o filhote, o que significa que não tem mais intenção de me ajudar.</t>
         </is>
       </c>
     </row>
@@ -4325,9 +4292,9 @@
           <t>You’re right that I cannot hand over Corgon. Before I say why, answer me this, Sorin. Are you still pursuing your research into the Magic Stone?</t>
         </is>
       </c>
-      <c r="L182" t="inlineStr">
-        <is>
-          <t>Está certo que não posso entregar Corgon. Antes de dizer por quê, responda-me, Sorin. Ainda está perseguindo sua pesquisa sobre a Pedra Mágica?</t>
+      <c r="L182" s="20" t="inlineStr">
+        <is>
+          <t>Tem razão, não posso entregar Corgon. Antes de dizer por quê, responda-me isto, Sorin. Ainda persegue sua pesquisa sobre a Pedra Mágica?</t>
         </is>
       </c>
     </row>
@@ -4344,17 +4311,17 @@
       </c>
       <c r="J183" s="26" t="inlineStr">
         <is>
-          <t>ふっ、当たり前でしょう。闇の奇形などという忌み名を持つ臭い体に魂を縛り、朽ちた古城の陰鬱な暗闇で生き続ける理由が、他にあるとでも思っているのですか？</t>
+          <t>ふっ、当たり前でしょう。闇の奇形などという忌み名を持つ臭い体に魂を縛り、朽ちた古塔の陰鬱な暗闇で生き続ける理由が、他にあるとでも思っているのですか？</t>
         </is>
       </c>
       <c r="K183" s="28" t="inlineStr">
         <is>
-          <t>Heh. But of course. What other reason have I to bind my soul to this stinking flesh they call “dark abomination”—and linger in the gloom of a rotting old castle?</t>
-        </is>
-      </c>
-      <c r="L183" t="inlineStr">
-        <is>
-          <t>Heh. Mas é claro. Que outro motivo eu teria para atar minha alma a esta carne fétida que chamam de “abominação das trevas”... e permanecer na escuridão de um velho castelo em decomposição?</t>
+          <t>Heh. But of course. What other reason have I to bind my soul to this stinking flesh they call “dark abomination”—and linger in the gloom of a rotting old tower?</t>
+        </is>
+      </c>
+      <c r="L183" s="20" t="inlineStr">
+        <is>
+          <t>Heh. Mas claro. Que outra razão teria para amarrar minha alma a esta carne fedorenta que chamam de "abominação das trevas", e permanecer na penumbra de uma torre velha e apodrecida?</t>
         </is>
       </c>
     </row>
@@ -4383,11 +4350,11 @@
 Yes, I have need of the Stone. To preserve the world as it is, there is but one way: to use the Stone’s power and call the gods back to earth.</t>
         </is>
       </c>
-      <c r="L184" t="inlineStr">
-        <is>
-          <t>Preciso desvendar o segredo da Pedra.
-...Os deuses partiram, e o mistério está se esvaindo do mundo. Todos os “seres antigos” caminham para uma morte lenta. O que significa que a própria magia morrerá.
-Sim, preciso da Pedra. Para preservar o mundo como ele é, só há um caminho: usar o poder da Pedra e chamar os deuses de volta à terra.</t>
+      <c r="L184" s="20" t="inlineStr">
+        <is>
+          <t>Eu preciso desvendar o segredo da Pedra.
+...Os deuses partiram, e o mistério está se esvaindo do mundo. Todos os "seres antigos" caminham para uma morte lenta. Ou seja, a magia em si morrerá.
+Sim, preciso da Pedra. Para preservar o mundo como é, há um só caminho: usar o poder da Pedra e chamar os deuses de volta à terra.</t>
         </is>
       </c>
     </row>
@@ -4752,17 +4719,17 @@
       </c>
       <c r="J196" s="33" t="inlineStr">
         <is>
-          <t>- 古城 -</t>
+          <t>- 古塔 -</t>
         </is>
       </c>
       <c r="K196" s="33" t="inlineStr">
         <is>
-          <t>- Old Castle -</t>
-        </is>
-      </c>
-      <c r="L196" t="inlineStr">
-        <is>
-          <t>- Velho Castelo -</t>
+          <t>- Old Tower -</t>
+        </is>
+      </c>
+      <c r="L196" s="20" t="inlineStr">
+        <is>
+          <t>- Torre Antiga -</t>
         </is>
       </c>
       <c r="M196" s="20" t="n"/>
@@ -5036,10 +5003,10 @@
 Whether in a hundred years or a thousand, I cannot say. But from the night the gods withdrew from the earth, an inescapable fate was set upon us.</t>
         </is>
       </c>
-      <c r="L198" t="inlineStr">
-        <is>
-          <t>Como você sabe, os “seres antigos” — e a própria fonte do mistério, a magia — estão desaparecendo do mundo.
-Se em cem anos ou mil, não posso dizer. Mas desde a noite em que os deuses se retiraram da terra, um destino inevitável foi traçado para nós.</t>
+      <c r="L198" s="20" t="inlineStr">
+        <is>
+          <t>Como sabe, os "seres antigos", e a própria fonte do mistério, a magia em si, estão se apagando do mundo.
+Se em cem anos ou mil, não posso dizer. Mas desde a noite em que os deuses se retiraram da terra, um destino inevitável se pôs sobre nós.</t>
         </is>
       </c>
     </row>
@@ -5064,10 +5031,10 @@
 But have you considered this: perhaps the world is merely returning to its native shape.</t>
         </is>
       </c>
-      <c r="L199" t="inlineStr">
-        <is>
-          <t>Exatamente... Eventualmente, o mito se tornará o conto de ninar de um velho contador de histórias, e os espíritos viverão apenas em livros ilustrados.
-Mas já considerou isto: talvez o mundo esteja apenas retornando à sua forma nativa.</t>
+      <c r="L199" s="20" t="inlineStr">
+        <is>
+          <t>Justo... Cedo ou tarde, o mito virará a história de dormir de um velho contador, e os espíritos viverão só em livros ilustrados.
+Mas já considerou isto: talvez o mundo esteja apenas voltando à sua forma nativa.</t>
         </is>
       </c>
     </row>
@@ -5092,10 +5059,10 @@
 ...The signs are plain already. The ancient Eulderna that once swept through Sierre Terre has lost its vigor. In the east, the New Kingdom of Yel rises, hoisting science as its banner. Magic is being demoted to “mere scholarship,” and many elder races will be driven by humans to extinction or chains.</t>
         </is>
       </c>
-      <c r="L200" t="inlineStr">
-        <is>
-          <t>Sua forma nativa — monótona, brutal, quase não valendo a pena viver.
-...Os sinais já são claros. A antiga Eulderna, que um dia varreu Sierre Terre, perdeu seu vigor. No leste, o Novo Reino de Yel se ergue, erguendo a ciência como sua bandeira. A magia está sendo rebaixada a “mero estudo”, e muitas raças ancestrais serão levadas à extinção ou às correntes pelos humanos.</t>
+      <c r="L200" s="20" t="inlineStr">
+        <is>
+          <t>A forma nativa: monótona, brutal, quase sem valor para se viver.
+...Os sinais já são claros. A antiga Eulderna que varreu Sierre Terre perdeu o vigor. No leste, o Novo Reino de Yel se ergue, hasteando a ciência como bandeira. A magia está sendo rebaixada a "mera erudição", e muitas raças antigas serão levadas pelos humanos à extinção ou às correntes.</t>
         </is>
       </c>
     </row>
@@ -5118,9 +5085,9 @@
           <t>Yes, the age of man is upon us. And the history of this planet makes it clear: as on Eyth Terre and Rem-Ido, humankind hurries along the road to ruin—never knowing the worth of what they seize and destory along the way.</t>
         </is>
       </c>
-      <c r="L201" t="inlineStr">
-        <is>
-          <t>Sim, a era do homem está sobre nós. E a história deste planeta deixa claro: como em Eyth Terre e Rem-Ido, a humanidade apressa-se pelo caminho da ruína — sem jamais conhecer o valor do que toma e destrói pelo caminho.</t>
+      <c r="L201" s="20" t="inlineStr">
+        <is>
+          <t>Sim, a era do homem chegou. E a história deste planeta deixa claro: como em Eyth Terre e Rem-Ido, a humanidade se apressa pela estrada da ruína, sem nunca saber o valor daquilo que toma e destrói pelo caminho.</t>
         </is>
       </c>
     </row>
@@ -5143,9 +5110,9 @@
           <t>Every civilization meets its end. Where some wither, others sprout anew. Don’t you think it’s a law that lies beyond our small measures of good and evil, Sorin?</t>
         </is>
       </c>
-      <c r="L202" t="inlineStr">
-        <is>
-          <t>Toda civilização encontra seu fim. Onde algumas murcham, outras brotam novamente. Não acha que é uma lei que está além de nossas pequenas medidas de bem e mal, Sorin?</t>
+      <c r="L202" s="20" t="inlineStr">
+        <is>
+          <t>Toda civilização encontra seu fim. Onde umas murcham, outras brotam. Não acha que é uma lei que está além das nossas pequenas medidas de bem e mal, Sorin?</t>
         </is>
       </c>
     </row>
@@ -5170,10 +5137,10 @@
 The rise and fall of men, good and ill—even the designs of the gods—none of it concerns me. I simply refuse to lose this power. This sorcery that once bent the world to my will is everything I am. To be robbed of it is intolerable.</t>
         </is>
       </c>
-      <c r="L203" t="inlineStr">
-        <is>
-          <t>Chega de enigmas. Falarei claramente.
-A ascensão e queda dos homens, o bem e o mal — até mesmo os desígnios dos deuses — nada disso me interessa. Simplesmente me recuso a perder este poder. Esta magia que um dia dobrou o mundo à minha vontade é tudo o que sou. Ser privado dela é intolerável.</t>
+      <c r="L203" s="20" t="inlineStr">
+        <is>
+          <t>Chega de enigmas. Falarei claro.
+A ascensão e queda dos homens, o bem e o mal, até mesmo os desígnios dos deuses: nada disso me importa. Eu simplesmente me recuso a perder este poder. Esta feitiçaria que um dia dobrou o mundo à minha vontade é tudo o que eu sou. Ser roubado dela é intolerável.</t>
         </is>
       </c>
     </row>
@@ -5189,7 +5156,7 @@
       <c r="J204" s="26" t="inlineStr">
         <is>
           <t>…師よ、二百年前、僕を殺さなかったのは何故ですか？　あなたも同じ船に乗ったものと、僕は思っていたのですがね。
-まさかこの城に、二百年前あなたが果たさなかったことを、果たしに来たのですか？　もっとも、今では僕の力は遥かに強大になっています。あなたよりも、ずっとね。</t>
+まさかこの塔に、二百年前あなたが果たさなかったことを、果たしに来たのですか？　もっとも、今では僕の力は遥かに強大になっています。あなたよりも、ずっとね。</t>
         </is>
       </c>
       <c r="K204" s="28" t="inlineStr">
@@ -5198,10 +5165,10 @@
 Or have you come today to finish what you failed to do then? Mind you, my power has grown—far beyond yours.</t>
         </is>
       </c>
-      <c r="L204" t="inlineStr">
-        <is>
-          <t>...Mestre, por que me poupou duzentos anos atrás? Pensei que navegássemos no mesmo barco.
-Ou veio hoje para terminar o que não conseguiu fazer naquela época? Esteja avisado, meu poder cresceu — muito além do seu.</t>
+      <c r="L204" s="20" t="inlineStr">
+        <is>
+          <t>...Mestre, por que me poupou há duzentos anos? Pensei que navegássemos no mesmo barco.
+Ou veio hoje terminar o que falhou em fazer então? Fique sabendo, meu poder cresceu: muito além do seu.</t>
         </is>
       </c>
     </row>
@@ -5226,10 +5193,10 @@
 ...I will kill the dragon child and take the Stone. Try to stop me if you like—it will avail you nothing.</t>
         </is>
       </c>
-      <c r="L205" t="inlineStr">
-        <is>
-          <t>As Pedras Mágicas, ditas forjadas pelos deuses na era antiga — se dominarmos todo o seu poder, podemos abrir os portões dos deuses e convocá-los de volta, detendo a “degeneração” do mundo.
-...Matarei a criança dragão e tomarei a Pedra. Tente me impedir, se quiser — de nada adiantará.</t>
+      <c r="L205" s="20" t="inlineStr">
+        <is>
+          <t>As Pedras Mágicas, dizem que foram forjadas pelos deuses na era antiga: se dominarmos todo o poder delas, podemos abrir os portões dos deuses e invocá-los de volta, detendo a "degeneração" do mundo.
+...Vou matar o filhote de dragão e tomar a Pedra. Tente me deter se quiser: não lhe servirá de nada.</t>
         </is>
       </c>
     </row>
@@ -5252,9 +5219,9 @@
           <t>Sorin... you are mistaken about one thing.</t>
         </is>
       </c>
-      <c r="L206" t="inlineStr">
-        <is>
-          <t>Sorin... você está enganado sobre uma coisa.</t>
+      <c r="L206" s="20" t="inlineStr">
+        <is>
+          <t>Sorin... você está errado sobre uma coisa.</t>
         </is>
       </c>
     </row>
@@ -5277,9 +5244,9 @@
           <t>Mistaken...?</t>
         </is>
       </c>
-      <c r="L207" t="inlineStr">
-        <is>
-          <t>Enganado...?</t>
+      <c r="L207" s="20" t="inlineStr">
+        <is>
+          <t>Errado...?</t>
         </is>
       </c>
     </row>
@@ -5302,9 +5269,9 @@
           <t>Your work on the Stone is already complete. I believe you’ve already “drawn out all it has to give.”</t>
         </is>
       </c>
-      <c r="L208" t="inlineStr">
-        <is>
-          <t>Seu trabalho com a Pedra já está completo. Creio que você já “extraiu tudo o que ela tinha a oferecer”.</t>
+      <c r="L208" s="20" t="inlineStr">
+        <is>
+          <t>Seu trabalho sobre a Pedra já está completo. Acredito que você já "extraiu tudo o que ela tem a dar".</t>
         </is>
       </c>
     </row>
@@ -5327,9 +5294,9 @@
           <t>Complete? Don’t be absurd. The Stone’s power is far beyond—</t>
         </is>
       </c>
-      <c r="L209" t="inlineStr">
-        <is>
-          <t>Completo? Não seja absurdo. O poder da Pedra está muito além—</t>
+      <c r="L209" s="20" t="inlineStr">
+        <is>
+          <t>Completo? Não seja absurdo. O poder da Pedra está muito além...</t>
         </is>
       </c>
     </row>
@@ -5352,9 +5319,9 @@
           <t>You do hold the Stone’s power. But—as you yourself must suspect—alas, even if you gathered the other two Stones, the strength you seek would still lie far beyond your reach.</t>
         </is>
       </c>
-      <c r="L210" t="inlineStr">
-        <is>
-          <t>Você detém o poder da Pedra. Mas — como você mesmo deve suspeitar — infelizmente, mesmo que reunisse as outras duas Pedras, a força que busca ainda estaria muito além do seu alcance.</t>
+      <c r="L210" s="20" t="inlineStr">
+        <is>
+          <t>Você tem, sim, o poder da Pedra. Mas, como você mesmo deve suspeitar, ai de você: mesmo se reunisse as outras duas Pedras, a força que busca ainda estaria muito além do seu alcance.</t>
         </is>
       </c>
     </row>
@@ -5381,11 +5348,11 @@
 The Stone’s hidden might will open the gods’ threshold and call them down—</t>
         </is>
       </c>
-      <c r="L211" t="inlineStr">
-        <is>
-          <t>Hah. E o que você saberia, Mestre — sem uma Pedra?
-É verdade, você já possuiu um conhecimento incomum sobre elas. Mas isso foi há muito tempo. Você está muito atrás do que aprendi em dois séculos.
-O poder oculto da Pedra abrirá o limiar dos deuses e os trará de volta—</t>
+      <c r="L211" s="20" t="inlineStr">
+        <is>
+          <t>Hah. E o que você saberia, Mestre, sem uma Pedra?
+Verdade, você um dia possuía um saber inquietante sobre elas. Mas isso foi há muito tempo. Você está muito atrás do que aprendi em dois séculos.
+O poder oculto da Pedra abrirá o umbral dos deuses e os chamará para baixo...</t>
         </is>
       </c>
     </row>
@@ -5408,9 +5375,9 @@
           <t>...If it were a true Magic Stone, yes. But what you hold is a counterfeit.</t>
         </is>
       </c>
-      <c r="L212" t="inlineStr">
-        <is>
-          <t>...Se fosse uma verdadeira Pedra Mágica, sim. Mas o que você possui é uma falsificação.</t>
+      <c r="L212" s="20" t="inlineStr">
+        <is>
+          <t>...Se fosse uma Pedra Mágica de verdade, sim. Mas o que você tem é uma contrafação.</t>
         </is>
       </c>
     </row>
@@ -5433,9 +5400,9 @@
           <t>Nonsense... Heh—surely you didn’t come all this way just to peddle such drivel?</t>
         </is>
       </c>
-      <c r="L213" t="inlineStr">
-        <is>
-          <t>Absurdo... Heh — certamente não veio até aqui só para espalhar essas bobagens?</t>
+      <c r="L213" s="20" t="inlineStr">
+        <is>
+          <t>Absurdo... Heh: por acaso veio até aqui só para vender papo furado?</t>
         </is>
       </c>
     </row>
@@ -5458,7 +5425,7 @@
           <t>Sorin, I made this Stone.</t>
         </is>
       </c>
-      <c r="L214" t="inlineStr">
+      <c r="L214" s="20" t="inlineStr">
         <is>
           <t>Sorin, eu fiz esta Pedra.</t>
         </is>
@@ -5483,7 +5450,7 @@
           <t>...</t>
         </is>
       </c>
-      <c r="L215" t="inlineStr">
+      <c r="L215" s="20" t="inlineStr">
         <is>
           <t>...</t>
         </is>
@@ -5508,9 +5475,9 @@
           <t>Master, since when did you stoop to such dreary jokes...?</t>
         </is>
       </c>
-      <c r="L216" t="inlineStr">
-        <is>
-          <t>Mestre, desde quando você se rebaixou a piadas tão sombrias assim...?</t>
+      <c r="L216" s="20" t="inlineStr">
+        <is>
+          <t>Mestre, desde quando o senhor se rebaixa a piadas tão melancólicas...?</t>
         </is>
       </c>
     </row>
@@ -5535,10 +5502,10 @@
 Then look into this eye, Sorin—see the curse etched in my socket, the curse without end. </t>
         </is>
       </c>
-      <c r="L217" t="inlineStr">
-        <is>
-          <t>Não o culpo por duvidar.
-Então olhe neste olho, Sorin—veja a maldição gravada em meu encaixe, a maldição sem fim.</t>
+      <c r="L217" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Não te culpo pela desconfiança.
+Então olhe neste olho, Sorin: veja a maldição gravada na minha órbita, a maldição sem fim. </t>
         </is>
       </c>
     </row>
@@ -5605,7 +5572,7 @@
           <t>...!!</t>
         </is>
       </c>
-      <c r="L222" t="inlineStr">
+      <c r="L222" s="20" t="inlineStr">
         <is>
           <t>...!!</t>
         </is>
@@ -5634,10 +5601,10 @@
 The Stones you and Corgon bear are failures I crafted long ago, imitations made to resemble this crystal.</t>
         </is>
       </c>
-      <c r="L223" t="inlineStr">
-        <is>
-          <t>Você deve ter ouvido a lenda de 《Aura’s Stone-Crystal》. Esta é a verdadeira Pedra Mágica, Sorin.
-As Pedras que você e Corgon carregam são fracassos que criei há muito tempo, imitações feitas para se assemelhar a este cristal.</t>
+      <c r="L223" s="20" t="inlineStr">
+        <is>
+          <t>Você deve conhecer o conto de 《Cristal-Pedra de Aura》. Esta é a verdadeira Pedra Mágica, Sorin.
+As Pedras que você e Corgon carregam são falhas que eu mesmo criei há muito tempo, imitações feitas para se parecer com este cristal.</t>
         </is>
       </c>
     </row>
@@ -5662,9 +5629,9 @@
           <t>Ridiculous... 《Aura’s Stone-Crystal》... the Eternal Eye...? That’s a myth—</t>
         </is>
       </c>
-      <c r="L224" t="inlineStr">
-        <is>
-          <t>Ridículo... 《Aura’s Stone-Crystal》... o Olho Eterno...? Isso é um mito—</t>
+      <c r="L224" s="20" t="inlineStr">
+        <is>
+          <t>Ridículo... 《Cristal-Pedra de Aura》... o Olho Eterno...? Isso é mito...</t>
         </is>
       </c>
     </row>
@@ -5689,9 +5656,9 @@
           <t xml:space="preserve">A myth... is it... real...? Then... </t>
         </is>
       </c>
-      <c r="L225" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Um mito... é real...? Então... </t>
+      <c r="L225" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Um mito... é... real...? Então... </t>
         </is>
       </c>
     </row>
@@ -5716,9 +5683,9 @@
           <t>Hah... heh heh... To think I missed it... So—that’s how it is...</t>
         </is>
       </c>
-      <c r="L226" t="inlineStr">
-        <is>
-          <t>Hah... heh heh... Pensar que eu não percebi... Então—é assim que é...</t>
+      <c r="L226" s="20" t="inlineStr">
+        <is>
+          <t>Hah... heh heh... E eu sem perceber... Então: é assim...</t>
         </is>
       </c>
     </row>
@@ -5747,11 +5714,11 @@
 Come, sit, Master. It seems we still have much to speak of. </t>
         </is>
       </c>
-      <c r="L227" t="inlineStr">
-        <is>
-          <t>“O Primeiro Alquimista.” Claro—você foi o começo de tudo.
-Muito antes da humanidade desta era respirar pela primeira vez, você já vivia. Não, talvez seja mais verdadeiro dizer que não podia morrer. Agora entendo—tanto o segredo do seu olho quanto a razão de não ter me matado.
-Venha, sente-se, Mestre. Parece que ainda temos muito o que conversar.</t>
+      <c r="L227" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"O Primeiro Alquimista." Claro: o senhor foi o começo de tudo.
+Muito antes de a humanidade desta era respirar pela primeira vez, você vivia. Não: talvez seja mais verdade dizer que você não podia morrer. Agora entendo: tanto o segredo do seu olho quanto a razão de não ter me matado.
+Venha, sente-se, Mestre. Parece que ainda temos muito de que falar. </t>
         </is>
       </c>
     </row>
@@ -6118,17 +6085,17 @@
       </c>
       <c r="J239" s="33" t="inlineStr">
         <is>
-          <t>- 古城 -</t>
+          <t>- 古塔 -</t>
         </is>
       </c>
       <c r="K239" s="33" t="inlineStr">
         <is>
-          <t>- Old Castle -</t>
-        </is>
-      </c>
-      <c r="L239" t="inlineStr">
-        <is>
-          <t>- Castelo Antigo -</t>
+          <t>- Old Tower -</t>
+        </is>
+      </c>
+      <c r="L239" s="20" t="inlineStr">
+        <is>
+          <t>- Torre Antiga -</t>
         </is>
       </c>
       <c r="M239" s="20" t="n"/>
@@ -6404,11 +6371,11 @@
 She fell in love with a mortal man and made herself prisoner in a house of stone. In time, she took wing with a fledgling that yearned for the sky and was exalted as a goddess. Yes, the birth of Lulwy.</t>
         </is>
       </c>
-      <c r="L241" t="inlineStr">
-        <is>
-          <t>Então a lenda era verdadeira, não era?
-...Na época em que ela ainda era um espírito da floresta, seu nome era Aura.
-Ela se apaixonou por um homem mortal e se aprisionou em uma casa de pedra. Com o tempo, alçou voo com um filhote que ansiava pelos céus e foi exaltada como uma deusa. Sim, o nascimento de Lulwy.</t>
+      <c r="L241" s="20" t="inlineStr">
+        <is>
+          <t>Então o conto era verdade, não era?
+...Nos dias em que ela ainda era um espírito da floresta, seu nome era Aura.
+Ela se apaixonou por um homem mortal e fez de si prisioneira numa casa de pedra. Com o tempo, voou com um filhote que ansiava pelo céu e foi exaltada como deusa. Sim, o nascimento de Lulwy.</t>
         </is>
       </c>
     </row>
@@ -6433,10 +6400,10 @@
 One account says that Aura—no, Lulwy—laid a cruel doom upon him. As a chastisement for having entrusted herself to a human heart, she took both his eyes so he could never behold her again, and set upon him the curse of undying. She knew the man would go on loving her—and therefore suffer, forever.</t>
         </is>
       </c>
-      <c r="L242" t="inlineStr">
-        <is>
-          <t>É um mito famoso, mas poucos livros falam do destino do homem mortal depois disso.
-Uma versão diz que Aura—não, Lulwy—lhe impôs um destino cruel. Como castigo por ter confiado seu coração a um humano, ela lhe tirou os dois olhos para que nunca mais pudesse contemplá-la e lançou sobre ele a maldição da imortalidade. Ela sabia que o homem continuaria a amá-la—e, portanto, sofreria para sempre.</t>
+      <c r="L242" s="20" t="inlineStr">
+        <is>
+          <t>É um mito famoso, mas poucos livros contam o destino do homem mortal depois.
+Um relato diz que Aura, não, Lulwy, lançou sobre ele uma condenação cruel. Como castigo por ter se entregado a um coração humano, tomou-lhe os dois olhos para que nunca mais pudesse vê-la, e impôs-lhe a maldição da imortalidade. Ela sabia que o homem continuaria a amá-la, e por isso sofreria, para sempre.</t>
         </is>
       </c>
     </row>
@@ -6461,10 +6428,10 @@
 Heh, what a thing... Master, to how many of the world’s scattered secrets have you been tied?</t>
         </is>
       </c>
-      <c r="L243" t="inlineStr">
-        <is>
-          <t>...A ascensão de Lulwy pertence a tempos antigos—alguns a chamam de “Era dos Começos”, a Segunda Era. Quantos anos se passaram desde então? Dezenas de milhões—centenas de milhões?
-Heh, que coisa... Mestre, a quantos dos segredos espalhados pelo mundo você esteve ligado?</t>
+      <c r="L243" s="20" t="inlineStr">
+        <is>
+          <t>...A ascensão de Lulwy pertence aos dias antigos: alguns chamam de "Era dos Começos", a Segunda Era. Quantos anos se passaram desde então? Dezenas de milhões? Centenas de milhões?
+Heh, que coisa... Mestre, a quantos dos segredos espalhados pelo mundo o senhor esteve atado?</t>
         </is>
       </c>
     </row>
@@ -6489,10 +6456,10 @@
 That legend, too—I likely wrote it myself, though I doubt it has reached you without error.</t>
         </is>
       </c>
-      <c r="L244" t="inlineStr">
-        <is>
-          <t>Só isso é certo: não são experiências que alguém deva invejar.
-Aquela lenda também—provavelmente a escrevi eu mesmo, embora duvide que tenha chegado até você sem erros.</t>
+      <c r="L244" s="20" t="inlineStr">
+        <is>
+          <t>Só isto é certo: não são experiências que alguém deveria invejar.
+Aquela lenda também: provavelmente fui eu mesmo quem a escreveu, embora duvide que tenha chegado até você sem erros.</t>
         </is>
       </c>
     </row>
@@ -6519,11 +6486,11 @@
 This eye is no grand punishment: it is merely her whim. To Lulwy, now a goddess, I am no more than a mote on the wind, beneath notice.</t>
         </is>
       </c>
-      <c r="L245" t="inlineStr">
-        <is>
-          <t>Sim, eu “tive a sorte” de vê-la naquela floresta, já como uma deusa.
-No instante em que ela voltou seu olhar para mim, este cristal foi gravado em meu encaixe. Não houve sentimento, nenhuma palavra, nada. Desde então, tenho vagado por uma noite sem fim, buscando sua voz—mas ela nunca mais apareceu diante de mim.
-Este olho não é um grande castigo: é apenas um capricho dela. Para Lulwy, agora uma deusa, não passo de um grão de poeira ao vento, algo insignificante.</t>
+      <c r="L245" s="20" t="inlineStr">
+        <is>
+          <t>Sim, eu "por acaso" a vi naquela floresta, já como deusa.
+No instante em que ela voltou o olhar para mim, este cristal foi gravado na minha órbita. Não havia sentimento nele, nem palavra, absolutamente nada. Desde então, vagueio por uma noite sem fim, buscando sua voz, mas ela nunca mais se apresentou a mim.
+Este olho não é castigo grandioso: é apenas o capricho dela. Para Lulwy, hoje uma deusa, eu não passo de um grão de poeira ao vento, sem a menor importância.</t>
         </is>
       </c>
     </row>
@@ -6546,9 +6513,9 @@
           <t>...Even so, this eye was my only thread to her. I nursed the faint hope that if I unraveled its secret, I might win her notice once more. By day and night I pursued the riddle of the stone, and in time that fervor drove me to imitation.</t>
         </is>
       </c>
-      <c r="L246" t="inlineStr">
-        <is>
-          <t>...Mesmo assim, este olho era meu único elo com ela. Eu alimentava a tênue esperança de que, se desvendasse seu segredo, poderia chamar sua atenção mais uma vez. Dia e noite, persisti no enigma da pedra, e com o tempo, essa obsessão me levou à imitação.</t>
+      <c r="L246" s="20" t="inlineStr">
+        <is>
+          <t>...Ainda assim, este olho foi meu único fio até ela. Alimentei a fraca esperança de que, se desvendasse seu segredo, poderia reconquistar sua atenção. Dia e noite perseguí o enigma da pedra, e com o tempo esse fervor me levou à imitação.</t>
         </is>
       </c>
     </row>
@@ -6573,10 +6540,10 @@
 ...At last I abandoned the mimicry, and the counterfeit Stones sank with the dust of history.</t>
         </is>
       </c>
-      <c r="L247" t="inlineStr">
-        <is>
-          <t>Ergui-me, antes que percebesse, para ser contado entre os grandes alquimistas. Mas a inteligência humana não alcança o milagre dos deuses. Nenhuma das incontáveis Pedras que forjei possuía o poder deste olho.
-...Por fim, abandonei a imitação, e as Pedras falsas afundaram com a poeira da história.</t>
+      <c r="L247" s="20" t="inlineStr">
+        <is>
+          <t>Cresci, sem perceber, a ser contado entre os grandes alquimistas. Mas a inteligência humana não alcança o milagre dos deuses. Nem uma das incontáveis Pedras que forgei carregou o poder deste olho.
+...Por fim abandonei a imitação, e as Pedras falsas afundaram com o pó da história.</t>
         </is>
       </c>
     </row>
@@ -6599,9 +6566,9 @@
           <t>...And yet, the three shards you created withstood the trial of time, and now stand revealed in this era. Is that not so?</t>
         </is>
       </c>
-      <c r="L248" t="inlineStr">
-        <is>
-          <t>...E ainda assim, os três fragmentos que você criou resistiram ao teste do tempo e agora se revelam nesta era. Não é assim?</t>
+      <c r="L248" s="20" t="inlineStr">
+        <is>
+          <t>...E no entanto, os três fragmentos que você criou resistiram à prova do tempo e agora se revelam nesta era. Não é assim?</t>
         </is>
       </c>
     </row>
@@ -6624,7 +6591,7 @@
           <t>...Ah. It is.</t>
         </is>
       </c>
-      <c r="L249" t="inlineStr">
+      <c r="L249" s="20" t="inlineStr">
         <is>
           <t>...Ah. É.</t>
         </is>
@@ -6641,20 +6608,20 @@
       </c>
       <c r="J250" s="26" t="inlineStr">
         <is>
-          <t>あなたの弟子が魔石を手に入れ、その力の虜となると、あなたは弟子の居城を訪れました。弟子思いの優しいあなたは、僕の魂を救うために、僕を殺しに来たのです。
+          <t>あなたの弟子が魔石を手に入れ、その力の虜となると、あなたは弟子の居塔を訪れました。弟子思いの優しいあなたは、僕の魂を救うために、僕を殺しに来たのです。
 しかし…僕の計画を知った時、あなたの中に葛藤が生じました。</t>
         </is>
       </c>
       <c r="K250" s="28" t="inlineStr">
         <is>
-          <t>When your disciple gained a Magic Stone and fell captive to its power, you came to his keep. Kind, solicitous Master that you are, you came to kill me—to save my soul.
+          <t>When your disciple gained a Magic Stone and fell captive to its power, you came to his tower. Kind, solicitous Master that you are, you came to kill me—to save my soul.
 But... when you learned of my plan, a struggle took root in you.</t>
         </is>
       </c>
-      <c r="L250" t="inlineStr">
-        <is>
-          <t>Quando seu discípulo obteve uma Pedra Mágica e caiu sob seu poder, você veio ao seu forte. Mestre bondoso e solícito que é, veio me matar—para salvar minha alma.
-Mas... quando soube do meu plano, uma luta se instalou em você.</t>
+      <c r="L250" s="20" t="inlineStr">
+        <is>
+          <t>Quando seu discípulo ganhou uma Pedra Mágica e caiu cativo do poder dela, você veio à torre dele. Mestre gentil e zeloso que é, veio me matar: para salvar minha alma.
+Mas... quando soube do meu plano, uma luta criou raiz em você.</t>
         </is>
       </c>
     </row>
@@ -6679,10 +6646,10 @@
 Perhaps you could be reunited with Lulwy, and learn the meaning of the curse laid upon your eye.</t>
         </is>
       </c>
-      <c r="L251" t="inlineStr">
-        <is>
-          <t>Você pensou que, se minha vasta magia fosse unida à Pedra, talvez os deuses pudessem realmente ser chamados de volta à terra.
-Talvez pudesse se reunir com Lulwy e descobrir o significado da maldição lançada sobre seu olho.</t>
+      <c r="L251" s="20" t="inlineStr">
+        <is>
+          <t>Você pensou que, se minha vasta feitiçaria se unisse à Pedra, talvez os deuses realmente pudessem ser chamados de volta à terra.
+Talvez você pudesse reencontrar Lulwy, e aprender o significado da maldição posta no seu olho.</t>
         </is>
       </c>
     </row>
@@ -6707,10 +6674,10 @@
 Sorin, I only wished to see Lulwy once more. </t>
         </is>
       </c>
-      <c r="L252" t="inlineStr">
-        <is>
-          <t>...O significado deste olho. Até isso, acho, pode não importar mais.
-Sorin, eu só queria ver Lulwy mais uma vez.</t>
+      <c r="L252" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">...O significado deste olho. Até isso, penso, pode já não importar.
+Sorin, eu só queria ver Lulwy mais uma vez. </t>
         </is>
       </c>
     </row>
@@ -6733,7 +6700,7 @@
           <t>...</t>
         </is>
       </c>
-      <c r="L253" t="inlineStr">
+      <c r="L253" s="20" t="inlineStr">
         <is>
           <t>...</t>
         </is>
@@ -6760,10 +6727,10 @@
 There is a dark fire banked in your breast that neither reason nor morality can cool. As with me, there is something you desire so fiercely you cannot let it go—no matter how the world might be changed.</t>
         </is>
       </c>
-      <c r="L254" t="inlineStr">
+      <c r="L254" s="20" t="inlineStr">
         <is>
           <t>Heh... heh heh... Mestre, parece que finalmente encontramos nossa semelhança.
-Há um fogo sombrio guardado em seu peito que nem a razão nem a moral podem apagar. Como eu, há algo que deseja com tanta ferocidade que não pode deixar ir—não importa como o mundo possa mudar.</t>
+Há um fogo escuro abafado no seu peito que nem a razão nem a moral conseguem esfriar. Como eu, há algo que você deseja tão ferozmente que não consegue largar, por mais que o mundo possa mudar.</t>
         </is>
       </c>
     </row>
@@ -6788,10 +6755,10 @@
 To debase yourself into a befouled abomination in pursuit of a counterfeit Stone—what a jest.</t>
         </is>
       </c>
-      <c r="L255" t="inlineStr">
-        <is>
-          <t>...E a vítima dessa ardente paixão sombria foi este corpo meu, não foi?
-Rebaixar-se a uma abominação profanada em busca de uma Pedra falsa—que piada.</t>
+      <c r="L255" s="20" t="inlineStr">
+        <is>
+          <t>...E a vítima desse ardor sombrio foi este meu corpo, foi?
+Rebaixar-se a uma abominação imunda atrás de uma Pedra falsa: que piada.</t>
         </is>
       </c>
     </row>
@@ -6814,7 +6781,7 @@
           <t>...I am sorry, Sorin.</t>
         </is>
       </c>
-      <c r="L256" t="inlineStr">
+      <c r="L256" s="20" t="inlineStr">
         <is>
           <t>...Sinto muito, Sorin.</t>
         </is>
@@ -6843,11 +6810,11 @@
 Now that the path of Stone-lore is cut off, the knowledge won by this flesh may prove my last hope.</t>
         </is>
       </c>
-      <c r="L257" t="inlineStr">
+      <c r="L257" s="20" t="inlineStr">
         <is>
           <t>Não, Mestre.
-...A ironia tem suas utilidades. Este corpo impuro não serviu apenas para prolongar minha vida miserável.
-Agora que o caminho do conhecimento das Pedras está cortado, o saber obtido por esta carne pode ser minha última esperança.</t>
+...A ironia tem seus usos. Este corpo imundo não serviu só para prolongar minha vida miserável.
+Agora que o caminho da ciência das Pedras está cortado, o conhecimento conquistado por esta carne pode ser minha última esperança.</t>
         </is>
       </c>
     </row>
@@ -6870,9 +6837,9 @@
           <t>What do you mean, Sorin?</t>
         </is>
       </c>
-      <c r="L258" t="inlineStr">
-        <is>
-          <t>O que você quer dizer, Sorin?</t>
+      <c r="L258" s="20" t="inlineStr">
+        <is>
+          <t>Como assim, Sorin?</t>
         </is>
       </c>
     </row>
@@ -6899,11 +6866,11 @@
 And since I have the power to seize the Stone if I choose, I think I still hold a card for negotiation.</t>
         </is>
       </c>
-      <c r="L259" t="inlineStr">
+      <c r="L259" s="20" t="inlineStr">
         <is>
           <t>Há segredos no reino dos mortos que nunca são sussurrados entre os vivos.
-Antes disso—um ponto a resolver. Agora que as Pedras se mostraram falsas, não faz sentido eu tomar a Pedra da criança dragão. “Quase” nenhum sentido. Pois a outra Pedra ainda desperta meu interesse.
-E como tenho o poder de tomar a Pedra se escolher, acho que ainda tenho uma carta para negociação.</t>
+Antes disso: um ponto a acertar. Agora que as Pedras se mostraram falsas, não há sentido em eu tomar a Pedra do filhote de dragão. "Quase" sem sentido. Porque a outra Pedra ainda desperta meu interesse.
+E como tenho o poder de tomá-la se quiser, acho que ainda seguro uma carta para a negociação.</t>
         </is>
       </c>
     </row>
@@ -6926,9 +6893,9 @@
           <t>So, you’re saying you want to ask me for a favor, is that it?</t>
         </is>
       </c>
-      <c r="L260" t="inlineStr">
-        <is>
-          <t>Então, você está dizendo que quer me pedir um favor, é isso?</t>
+      <c r="L260" s="20" t="inlineStr">
+        <is>
+          <t>Então está dizendo que quer me pedir um favor, é isso?</t>
         </is>
       </c>
     </row>
@@ -6951,9 +6918,9 @@
           <t>I’m glad you’re a man of understanding. It’s a simple errand.</t>
         </is>
       </c>
-      <c r="L261" t="inlineStr">
-        <is>
-          <t>Fico feliz que seja um homem compreensivo. É um simples recado.</t>
+      <c r="L261" s="20" t="inlineStr">
+        <is>
+          <t>Fico contente que seja um homem de entendimento. É um recado simples.</t>
         </is>
       </c>
     </row>
@@ -6968,7 +6935,7 @@
       </c>
       <c r="J262" s="26" t="inlineStr">
         <is>
-          <t>この古城から少し離れた沼地に、誰も寄り付かない洞窟があります。「死者の洞窟」と呼ばれるその洞窟の奥には、死者に守られ、しかし死者が決して近づくことのできない「淀み」があるのです。
+          <t>この古塔から少し離れた沼地に、誰も寄り付かない洞窟があります。「死者の洞窟」と呼ばれるその洞窟の奥には、死者に守られ、しかし死者が決して近づくことのできない「淀み」があるのです。
 …この瓶をあなたに渡しましょう。
 あなたには、この瓶に入っている液体の雫を一滴、この「淀み」に垂らしてきてほしいのです。
 …どうです、簡単でしょう？</t>
@@ -6976,16 +6943,16 @@
       </c>
       <c r="K262" s="28" t="inlineStr">
         <is>
-          <t>A short way from this castle, in the marsh, there is a cave shunned by all. They call it the “Crypt of the Damned.” In its depths lies a “pool of stagnation,” warded by the dead—yet one the dead themselves can never approach.
+          <t>A short way from this tower, in the marsh, there is a cave shunned by all. They call it the “Crypt of the Damned.” In its depths lies a “pool of stagnation,” warded by the dead—yet one the dead themselves can never approach.
 ...Take this vial.
 I want you to let a single drop of the liquid within fall into that pool. ...There, simple enough?</t>
         </is>
       </c>
-      <c r="L262" t="inlineStr">
-        <is>
-          <t>A uma curta distância deste castelo, no pântano, há uma caverna evitada por todos. Eles a chamam de “Cripta dos Condenados”. Em suas profundezas, há uma “poça de estagnação”, guardada pelos mortos—mas que os próprios mortos nunca podem se aproximar.
-...Pegue este frasco.
-Quero que deixe cair uma única gota do líquido dentro naquela poça. ...Simples assim?</t>
+      <c r="L262" s="20" t="inlineStr">
+        <is>
+          <t>A pouca distância desta torre, no pântano, há uma caverna evitada por todos. Chamam de "Cripta dos Condenados". Em seu fundo jaz uma "poça de estagnação", guardada pelos mortos, mas que os próprios mortos jamais podem se aproximar.
+...Tome este frasco.
+Quero que deixe uma única gota do líquido dentro cair naquela poça. ...Simples o bastante?</t>
         </is>
       </c>
     </row>
@@ -7012,11 +6979,11 @@
 The drop’s effect will not ripen for centuries. I swear no harm will come to your companions. Think of it as the price for the dragon child’s life—doesn’t that strike you as a fair bargain, Master?</t>
         </is>
       </c>
-      <c r="L263" t="inlineStr">
-        <is>
-          <t>Claro, para descer às profundezas da Cripta dos Condenados, você precisará de alguma força. Consulte o aventureiro que estava com você.
-Heh, essa sua expressão é natural—mas não posso lhe contar mais sobre o segredo.
-O efeito da gota não amadurecerá por séculos. Juro que nenhum mal virá aos seus companheiros. Pense nisso como o preço pela vida da criança dragão—não acha um acordo justo, Mestre?</t>
+      <c r="L263" s="20" t="inlineStr">
+        <is>
+          <t>Claro, para descer ao fundo da Cripta dos Condenados será preciso alguma força. Consulte o aventureiro que estava com você.
+Heh, essa sua cara é natural, mas não posso contar mais do segredo.
+O efeito da gota não amadurecerá por séculos. Juro que nenhum mal alcançará seus companheiros. Pense nisso como o preço da vida do filhote de dragão: não lhe parece uma barganha justa, Mestre?</t>
         </is>
       </c>
     </row>
@@ -7039,7 +7006,7 @@
           <t>...</t>
         </is>
       </c>
-      <c r="L264" t="inlineStr">
+      <c r="L264" s="20" t="inlineStr">
         <is>
           <t>...</t>
         </is>
@@ -7238,9 +7205,9 @@
           <t>...Look, Kettle.</t>
         </is>
       </c>
-      <c r="L284" t="inlineStr">
-        <is>
-          <t>...Olhe, Chaleira.</t>
+      <c r="L284" s="20" t="inlineStr">
+        <is>
+          <t>...Olhe, Kettle.</t>
         </is>
       </c>
     </row>
@@ -7263,7 +7230,7 @@
           <t>Mokyu?</t>
         </is>
       </c>
-      <c r="L285" t="inlineStr">
+      <c r="L285" s="20" t="inlineStr">
         <is>
           <t>Mokyu?</t>
         </is>
@@ -7288,9 +7255,9 @@
           <t>Welcome back, Kettle!</t>
         </is>
       </c>
-      <c r="L286" t="inlineStr">
-        <is>
-          <t>Bem-vinda de volta, Chaleira!</t>
+      <c r="L286" s="20" t="inlineStr">
+        <is>
+          <t>Bem-vindo de volta, Kettle!</t>
         </is>
       </c>
     </row>
@@ -7309,7 +7276,7 @@
           <t>I’m home, Quruitzia, Corgon.</t>
         </is>
       </c>
-      <c r="L287" t="inlineStr">
+      <c r="L287" s="20" t="inlineStr">
         <is>
           <t>Cheguei, Quruitzia, Corgon.</t>
         </is>
@@ -7334,9 +7301,9 @@
           <t>You look troubled... Did it go badly, after all?</t>
         </is>
       </c>
-      <c r="L288" t="inlineStr">
-        <is>
-          <t>Você parece preocupada... As coisas deram errado, afinal?</t>
+      <c r="L288" s="20" t="inlineStr">
+        <is>
+          <t>Você parece preocupado... Deu errado, afinal?</t>
         </is>
       </c>
     </row>
@@ -7357,10 +7324,10 @@
 Well, can you gather everyone first, Quruitzia?</t>
         </is>
       </c>
-      <c r="L289" t="inlineStr">
-        <is>
-          <t>Não, não são más notícias. É só que...
-Bem, você pode reunir todo mundo primeiro, Quruitzia?</t>
+      <c r="L289" s="20" t="inlineStr">
+        <is>
+          <t>Não, não é má notícia. É só que...
+Bom, pode reunir todo mundo primeiro, Quruitzia?</t>
         </is>
       </c>
     </row>
@@ -7383,7 +7350,7 @@
           <t>Mokyu...</t>
         </is>
       </c>
-      <c r="L290" t="inlineStr">
+      <c r="L290" s="20" t="inlineStr">
         <is>
           <t>Mokyu...</t>
         </is>
@@ -7446,9 +7413,9 @@
           <t>...and that’s how it is.</t>
         </is>
       </c>
-      <c r="L295" t="inlineStr">
-        <is>
-          <t>...e é assim que as coisas são.</t>
+      <c r="L295" s="20" t="inlineStr">
+        <is>
+          <t>...e é assim que ficou.</t>
         </is>
       </c>
     </row>
@@ -7471,9 +7438,9 @@
           <t>I see. So, in exchange for Corgon’s safety, we’re to drip a single drop from that vial into this so-called “pool of stagnation.”</t>
         </is>
       </c>
-      <c r="L296" t="inlineStr">
-        <is>
-          <t>Entendo. Então, em troca da segurança de Corgon, devemos pingar uma única gota daquele frasco neste tal “poço da estagnação”.</t>
+      <c r="L296" s="20" t="inlineStr">
+        <is>
+          <t>Entendi. Então, em troca da segurança do Corgon, devemos pingar uma única gota daquele frasco nesta tal "poça de estagnação".</t>
         </is>
       </c>
     </row>
@@ -7496,9 +7463,9 @@
           <t>Hm... Of course we’d need #pc’s help to explore the cave, but if there’s no danger in letting the drop fall, it doesn’t sound like a poor bargain.</t>
         </is>
       </c>
-      <c r="L297" t="inlineStr">
-        <is>
-          <t>Hm... Claro que precisaríamos da ajuda de #pc para explorar a caverna, mas se não há perigo em deixar a gota cair, não parece um mau acordo.</t>
+      <c r="L297" s="20" t="inlineStr">
+        <is>
+          <t>Hum... Claro que precisaríamos da ajuda do #pc para explorar a caverna, mas se não há perigo em deixar a gota cair, não me soa um mau acordo.</t>
         </is>
       </c>
     </row>
@@ -7521,9 +7488,9 @@
           <t>No. We mustn’t. Mixing what’s in that vial with the “pool of stagnation” is absolutely a bad idea.</t>
         </is>
       </c>
-      <c r="L298" t="inlineStr">
-        <is>
-          <t>Não. Não devemos. Misturar o que há naquele frasco com o “poço da estagnação” é uma péssima ideia.</t>
+      <c r="L298" s="20" t="inlineStr">
+        <is>
+          <t>Não. Não devemos. Misturar o que há naquele frasco com a "poça de estagnação" é absolutamente uma má ideia.</t>
         </is>
       </c>
     </row>
@@ -7546,7 +7513,7 @@
           <t>Lady Farris, but...</t>
         </is>
       </c>
-      <c r="L299" t="inlineStr">
+      <c r="L299" s="20" t="inlineStr">
         <is>
           <t>Lady Farris, mas...</t>
         </is>
@@ -7577,12 +7544,12 @@
 Lord Loytel, the “pool” is not for mortal hands to touch.</t>
         </is>
       </c>
-      <c r="L300" t="inlineStr">
-        <is>
-          <t>Por favor, ouça-me, Lorde Loytel. Há maldade enovelada neste acordo.
-Existe uma antiga lenda sobre a Cripta dos Condenados.
-Há muito tempo, “O Impuro” habitava lá e realizava rituais tão terríveis que gelavam o sangue. Aquela abominação ameaçava a terra — e até mesmo o reino divino — até que os deuses a destruíram. No entanto, a carne e o sangue da criatura derreteram-se nas profundezas da caverna e formaram um poço negro que nunca seca.
-Lorde Loytel, o “poço” não é para mãos mortais tocarem.</t>
+      <c r="L300" s="20" t="inlineStr">
+        <is>
+          <t>Por favor, ouça-me, Lorde Loytel. Há maldade enroscada neste acordo.
+Há uma lenda antiga sobre a Cripta dos Condenados.
+Há muito tempo, "O Impuro" habitava ali e realizava ritos tão horripilantes que gelavam o sangue. Aquela abominação ameaçava a terra, e até o reino divino, até que os deuses a destruíram. Ainda assim, a carne e o sangue da criatura se derreteram no fundo da caverna e formaram uma poça negra que nunca seca.
+Lorde Loytel, a "poça" não é para mãos mortais tocarem.</t>
         </is>
       </c>
     </row>
@@ -7609,11 +7576,11 @@
 Truly, if we accept Issizzle’s request, we’ll be leaving behind a monstrous curse for a later age.</t>
         </is>
       </c>
-      <c r="L301" t="inlineStr">
-        <is>
-          <t>Uma história assustadora, de fato... Mas espere, acho que estou entendendo agora.
-A única gota que devemos lançar naquele poço é uma semente do mal que brotará daqui a séculos. Um mal tão grande que os próprios deuses não poderão ignorá-lo... uma isca para atraí-los de volta à terra. Deve ser isso.
-Verdadeiramente, se aceitarmos o pedido de Issizzle, estaremos deixando para trás uma maldição monstruosa para uma era futura.</t>
+      <c r="L301" s="20" t="inlineStr">
+        <is>
+          <t>Um conto medonho de verdade... Mas espere, acho que estou vendo.
+A única gota que devemos lançar naquela poça é uma semente do mal que vai brotar daqui a séculos. Um mal tão grande que nem os deuses podem ignorar... isca para atraí-los de volta à terra. Deve ser isso.
+Sinceramente, se aceitarmos o pedido de Issizzle, deixaremos uma maldição monstruosa para uma era futura.</t>
         </is>
       </c>
     </row>
@@ -7636,9 +7603,9 @@
           <t>...And yet, by Kettle’s account, Issizzle is a sorcerer of terrifying reach. If we refuse this bargain, can we protect the little dragon from him with our strength alone?</t>
         </is>
       </c>
-      <c r="L302" t="inlineStr">
-        <is>
-          <t>...E ainda assim, segundo o relato de Kettle, Issizzle é um feiticeiro de alcance aterrador. Se recusarmos este acordo, poderemos proteger o pequeno dragão dele apenas com nossa força?</t>
+      <c r="L302" s="20" t="inlineStr">
+        <is>
+          <t>...E no entanto, pelo relato de Kettle, Issizzle é um feiticeiro de alcance aterrorizante. Se recusarmos este acordo, conseguimos proteger o dragonzinho contra ele só com a nossa força?</t>
         </is>
       </c>
     </row>
@@ -7661,7 +7628,7 @@
           <t>Mokyu...</t>
         </is>
       </c>
-      <c r="L303" t="inlineStr">
+      <c r="L303" s="20" t="inlineStr">
         <is>
           <t>Mokyu...</t>
         </is>
@@ -7688,10 +7655,10 @@
 We’ll take this vial instead.</t>
         </is>
       </c>
-      <c r="L304" t="inlineStr">
+      <c r="L304" s="20" t="inlineStr">
         <is>
           <t>Não, o acordo não precisa ser recusado. Tenho uma ideia, Lorde Loytel.
-Vamos ficar com este frasco em vez daquele.</t>
+Levaremos este frasco no lugar.</t>
         </is>
       </c>
     </row>
@@ -7714,9 +7681,9 @@
           <t>“Instead”? What is this vial? It does look very much like the one Issizzle gave us.</t>
         </is>
       </c>
-      <c r="L305" t="inlineStr">
-        <is>
-          <t>“Em vez daquele”? O que há neste frasco? Ele parece muito com o que Issizzle nos deu.</t>
+      <c r="L305" s="20" t="inlineStr">
+        <is>
+          <t>"No lugar"? Que frasco é este? Parece bem parecido com o que Issizzle nos deu.</t>
         </is>
       </c>
     </row>
@@ -7741,10 +7708,10 @@
 Right, you mean to purify the pool with a sacred drop. As expected of you, Lady Farris... though where in the world did you get such a thing?</t>
         </is>
       </c>
-      <c r="L306" t="inlineStr">
-        <is>
-          <t>Hm... mas tem um aroma muito puro. Seria algum tipo de água benta?
-Certo, você pretende purificar o poço com uma gota sagrada. Como esperado de você, Lady Farris... embora onde no mundo conseguiu algo assim?</t>
+      <c r="L306" s="20" t="inlineStr">
+        <is>
+          <t>Hum... mas tem um cheiro puríssimo. É alguma forma de água benta?
+Certinho, você quer purificar a poça com uma gota sagrada. À altura de você, Lady Farris... mas onde no mundo você arrumou uma coisa dessas?</t>
         </is>
       </c>
     </row>
@@ -7780,7 +7747,7 @@
           <t>...</t>
         </is>
       </c>
-      <c r="L308" t="inlineStr">
+      <c r="L308" s="20" t="inlineStr">
         <is>
           <t>...</t>
         </is>
@@ -7811,9 +7778,9 @@
           <t>In any case, it smells wonderful. So clean, so fresh, almost like... well, like newly washed...</t>
         </is>
       </c>
-      <c r="L310" t="inlineStr">
-        <is>
-          <t>De qualquer forma, cheira maravilhosamente. Tão limpo, tão fresco, quase como... bem, como algo recém-lavado...</t>
+      <c r="L310" s="20" t="inlineStr">
+        <is>
+          <t>De todo jeito, cheira maravilhosamente. Tão limpo, tão fresco, quase como... bom, como recém-lavado...</t>
         </is>
       </c>
     </row>
@@ -7836,7 +7803,7 @@
           <t>...</t>
         </is>
       </c>
-      <c r="L311" t="inlineStr">
+      <c r="L311" s="20" t="inlineStr">
         <is>
           <t>...</t>
         </is>
@@ -7861,7 +7828,7 @@
           <t>...</t>
         </is>
       </c>
-      <c r="L312" t="inlineStr">
+      <c r="L312" s="20" t="inlineStr">
         <is>
           <t>...</t>
         </is>
@@ -7886,9 +7853,9 @@
           <t xml:space="preserve">Perhaps I shouldn’t ask what it is. Better not to be boorish. In any event, it’s a clever plan, Lady Farris. </t>
         </is>
       </c>
-      <c r="L313" t="inlineStr">
-        <is>
-          <t>Talvez eu não devesse perguntar o que é. Melhor não ser grosseiro. De qualquer forma, é um plano inteligente, Lady Farris.</t>
+      <c r="L313" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Talvez eu não devesse perguntar o que é. Melhor não ser grosso. De todo modo, é um plano esperto, Lady Farris. </t>
         </is>
       </c>
     </row>
@@ -7911,9 +7878,9 @@
           <t>At the very least, a drop from this vial will not call a dark god back into the world.</t>
         </is>
       </c>
-      <c r="L314" t="inlineStr">
-        <is>
-          <t>No mínimo, uma gota deste frasco não invocará um deus das trevas de volta ao mundo.</t>
+      <c r="L314" s="20" t="inlineStr">
+        <is>
+          <t>No mínimo, uma gota deste frasco não chamará um deus sombrio de volta ao mundo.</t>
         </is>
       </c>
     </row>
@@ -7936,7 +7903,7 @@
           <t>R-right. Quite so.</t>
         </is>
       </c>
-      <c r="L315" t="inlineStr">
+      <c r="L315" s="20" t="inlineStr">
         <is>
           <t>C-certo. Exatamente.</t>
         </is>
@@ -7961,7 +7928,11 @@
           <t>...</t>
         </is>
       </c>
-      <c r="L316" t="inlineStr"/>
+      <c r="L316" s="20" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
     </row>
     <row r="317" ht="13.8" customHeight="1" s="21">
       <c r="G317" s="25" t="inlineStr">
@@ -7982,7 +7953,11 @@
           <t>...</t>
         </is>
       </c>
-      <c r="L317" t="inlineStr"/>
+      <c r="L317" s="20" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
     </row>
     <row r="318" ht="113.4" customHeight="1" s="21">
       <c r="G318" s="25" t="inlineStr">
@@ -7998,7 +7973,7 @@
           <t>お、おほん…ということだ、#pcよ。
 この決断は私には荷が重い。お前に任せよう。
 死者の洞窟に赴き、「淀み」を見つけるんだ。そこでイスシズルに渡されたこの瓶を使うか、あるいはファリスさんに渡された「聖水」を使うか…それはお前次第だ、よく考えてくれ。
-…安心しろ、私もついていってやる。お前だけに責任を追わせるのは酷だからな。</t>
+…安心しろ、私もついていってやる。お前だけに責任を負わせるのは酷だからな。</t>
         </is>
       </c>
       <c r="K318" s="28" t="inlineStr">
@@ -8009,12 +7984,12 @@
 ...You won’t go alone—I’ll come as well. It would be cruel to place such a burden entirely on your shoulders.</t>
         </is>
       </c>
-      <c r="L318" t="inlineStr">
-        <is>
-          <t>A-hã... Então, #pc.
-Essa decisão é pesada demais para eu tomar sozinho; eu a deixo com você.
-Vá até a Cripta dos Malditos e encontre a “poça da estagnação”. Lá, você poderá usar o frasco que Issizzle nos confiou ou a “água benta” que a Lady Farris forneceu... a escolha é sua. Pense bem.
-...Você não irá sozinho—eu também vou. Seria cruel colocar todo esse fardo sobre seus ombros.</t>
+      <c r="L318" s="20" t="inlineStr">
+        <is>
+          <t>Hem-hem... Então, #pc.
+Esta decisão é pesada demais para mim sozinho; deixo com você.
+Vá até a Cripta dos Condenados e encontre a "poça de estagnação". Lá, você pode usar o frasco que Issizzle nos confiou, ou a "água benta" que a Lady Farris forneceu... a escolha é sua. Pense bem.
+...Você não irá sozinho: eu vou também. Seria cruel colocar um fardo desses inteirinho nos seus ombros.</t>
         </is>
       </c>
     </row>
@@ -8155,10 +8130,10 @@
 Black and murky... just looking into it feels like it might swallow me whole.</t>
         </is>
       </c>
-      <c r="L335" t="inlineStr">
-        <is>
-          <t>Então é esta a "Poça".
-Negra e turva... só de olhar para ela, sinto que pode me engolir por inteiro.</t>
+      <c r="L335" s="20" t="inlineStr">
+        <is>
+          <t>Então esta é a "Poça".
+Preta e turva... só de olhar já sinto que ela pode me engolir inteiro.</t>
         </is>
       </c>
     </row>
@@ -8182,9 +8157,9 @@
           <t>What a dreadful place. Let’s finish Issizzle’s errand and leave at once.</t>
         </is>
       </c>
-      <c r="L336" t="inlineStr">
-        <is>
-          <t>Que lugar horrível. Vamos terminar o recado de Issizzle e sair daqui imediatamente.</t>
+      <c r="L336" s="20" t="inlineStr">
+        <is>
+          <t>Que lugar medonho. Vamos terminar o recado de Issizzle e ir embora já.</t>
         </is>
       </c>
     </row>
@@ -8215,10 +8190,10 @@
 Just dripping a single drop into this "Pool". A simple task.</t>
         </is>
       </c>
-      <c r="L338" t="inlineStr">
-        <is>
-          <t>Não poderia concordar mais.
-Basta pingar uma única gota nesta "Poça". Uma tarefa simples.</t>
+      <c r="L338" s="20" t="inlineStr">
+        <is>
+          <t>Concordo plenamente.
+É só pingar uma única gota nesta "Poça". Tarefa simples.</t>
         </is>
       </c>
     </row>
@@ -8256,11 +8231,11 @@
 (Lady Farris ended up coming along, but don’t worry. Whichever one you choose, I’ll make sure she never finds out. I’ll respect your decision.)</t>
         </is>
       </c>
-      <c r="L340" t="inlineStr">
-        <is>
-          <t>Então, #pc, qual frasco você vai usar? Este sinistro que Issizzle nos deu ou o... da água benta da Lady Farris?
-(...#pc, está me ouvindo?)
-(A Lady Farris acabou vindo junto, mas não se preocupe. Independentemente da sua escolha, eu garanto que ela nunca descobrirá. Respeitarei sua decisão.)</t>
+      <c r="L340" s="20" t="inlineStr">
+        <is>
+          <t>Então, #pc, qual frasco você vai usar? Este sinistro que Issizzle nos deu, ou o da Lady Farris... a água benta?
+(...#pc, você está me ouvindo?)
+(A Lady Farris acabou vindo junto, mas não se preocupe. Escolha o que escolher, vou garantir que ela nunca fique sabendo. Vou respeitar sua decisão.)</t>
         </is>
       </c>
     </row>
@@ -8289,7 +8264,7 @@
           <t>Use Issizzle’s bottle.</t>
         </is>
       </c>
-      <c r="L341" t="inlineStr">
+      <c r="L341" s="20" t="inlineStr">
         <is>
           <t>Usar o frasco de Issizzle.</t>
         </is>
@@ -8320,7 +8295,7 @@
           <t>Use Farris’s bottle.</t>
         </is>
       </c>
-      <c r="L342" t="inlineStr">
+      <c r="L342" s="20" t="inlineStr">
         <is>
           <t>Usar o frasco de Farris.</t>
         </is>
@@ -8358,10 +8333,10 @@
 It reeks of corruption. This single drop will no doubt nurture something wicked.</t>
         </is>
       </c>
-      <c r="L344" t="inlineStr">
+      <c r="L344" s="20" t="inlineStr">
         <is>
           <t>...Este é o frasco de Issizzle, certo?
-Cheira a corrupção. Essa única gota sem dúvida alimentará algo maligno.</t>
+Cheira a podridão. Esta única gota, sem dúvida, nutrirá algo perverso.</t>
         </is>
       </c>
     </row>
@@ -8390,7 +8365,7 @@
           <t>Yes.</t>
         </is>
       </c>
-      <c r="L345" t="inlineStr">
+      <c r="L345" s="20" t="inlineStr">
         <is>
           <t>Sim.</t>
         </is>
@@ -8421,7 +8396,7 @@
           <t>No.</t>
         </is>
       </c>
-      <c r="L346" t="inlineStr">
+      <c r="L346" s="20" t="inlineStr">
         <is>
           <t>Não.</t>
         </is>
@@ -8459,10 +8434,10 @@
 It smells... wonderful. I can’t even guess what this one drop will bring.</t>
         </is>
       </c>
-      <c r="L348" t="inlineStr">
+      <c r="L348" s="20" t="inlineStr">
         <is>
           <t>...Este é o frasco da Lady Farris, certo?
-Tem um cheiro... maravilhoso. Não consigo nem imaginar o que essa única gota trará.</t>
+Cheira... maravilhosamente. Não faço nem ideia do que essa única gota trará.</t>
         </is>
       </c>
     </row>
@@ -8491,7 +8466,7 @@
           <t>Yes.</t>
         </is>
       </c>
-      <c r="L349" t="inlineStr">
+      <c r="L349" s="20" t="inlineStr">
         <is>
           <t>Sim.</t>
         </is>
@@ -8522,7 +8497,7 @@
           <t>No.</t>
         </is>
       </c>
-      <c r="L350" t="inlineStr">
+      <c r="L350" s="20" t="inlineStr">
         <is>
           <t>Não.</t>
         </is>
@@ -8589,10 +8564,10 @@
 No, #pc, let me do at least this much. I can’t let you bear all the burdens alone.</t>
         </is>
       </c>
-      <c r="L355" t="inlineStr">
-        <is>
-          <t>Tudo certo. Vou pingar uma única gota deste frasco na "Poça".
-Não, #pc, deixe que eu faça pelo menos isso. Não posso deixar que carregue todos os fardos sozinho.</t>
+      <c r="L355" s="20" t="inlineStr">
+        <is>
+          <t>Muito bem. Vou pingar uma única gota deste frasco na "Poça".
+Não, #pc, deixe que eu faça pelo menos isto. Não posso deixar você carregar todos os fardos sozinho.</t>
         </is>
       </c>
     </row>
@@ -8618,10 +8593,10 @@
 And this floor, it’s really slimy and...</t>
         </is>
       </c>
-      <c r="L356" t="inlineStr">
+      <c r="L356" s="20" t="inlineStr">
         <is>
           <t>...Pensar que uma única gota pode mudar o destino do mundo... é quase sufocante.
-E este chão, está realmente viscoso e...</t>
+E este chão, é bem grudento e...</t>
         </is>
       </c>
     </row>
@@ -8659,9 +8634,9 @@
           <t>Agh!!</t>
         </is>
       </c>
-      <c r="L358" t="inlineStr">
-        <is>
-          <t>Agh!!</t>
+      <c r="L358" s="20" t="inlineStr">
+        <is>
+          <t>Ah!!</t>
         </is>
       </c>
     </row>
@@ -8690,7 +8665,7 @@
           <t>...</t>
         </is>
       </c>
-      <c r="L360" t="inlineStr">
+      <c r="L360" s="20" t="inlineStr">
         <is>
           <t>...</t>
         </is>
@@ -8716,7 +8691,7 @@
           <t>...</t>
         </is>
       </c>
-      <c r="L361" t="inlineStr">
+      <c r="L361" s="20" t="inlineStr">
         <is>
           <t>...</t>
         </is>
@@ -8774,11 +8749,11 @@
 Wait... where did both bottles go?</t>
         </is>
       </c>
-      <c r="L364" t="inlineStr">
+      <c r="L364" s="20" t="inlineStr">
         <is>
           <t>C-Calma, estou bem!
-...Ufa. Estou encharcada da cabeça aos pés. É horrível, mas pelo menos a "Poça" não era tão funda.
-Espere... para onde foram as duas garrafas?</t>
+...Ufa. Fiquei encharcado da cabeça aos pés. É horrível, mas pelo menos a "Poça" não era tão funda.
+Espera... para onde foram os dois frascos?</t>
         </is>
       </c>
     </row>
@@ -8830,7 +8805,7 @@
       </c>
       <c r="L366" t="inlineStr">
         <is>
-          <t>Lady Farris, acalme-se...</t>
+          <t>Lady Farris, calma...</t>
         </is>
       </c>
     </row>
@@ -8856,7 +8831,7 @@
       </c>
       <c r="L367" t="inlineStr">
         <is>
-          <t>Atrás — atrás de você!</t>
+          <t>Atrás... atrás de você!</t>
         </is>
       </c>
     </row>
@@ -8960,7 +8935,7 @@
       <c r="L376" t="inlineStr">
         <is>
           <t>...RU=VA SHE=NUR AZZALUU=RU... NE=IF DALOON... SA=RA KUN=AGRA...
-...RU=VA SHE... L’E=NOR SHA=RAGUN... HA=ZA...!!</t>
+...RU=VA SHE... L'E=NOR SHA=RAGUN... HA=ZA...!!</t>
         </is>
       </c>
     </row>
@@ -8986,7 +8961,7 @@
       </c>
       <c r="L377" t="inlineStr">
         <is>
-          <t>O qu—</t>
+          <t>O-quê...</t>
         </is>
       </c>
     </row>
@@ -9012,7 +8987,7 @@
       </c>
       <c r="L378" t="inlineStr">
         <is>
-          <t>Não faço ideia do que está dizendo, mas parece furioso.</t>
+          <t>Não faço ideia do que ele está dizendo, mas parece furioso.</t>
         </is>
       </c>
     </row>
@@ -9064,7 +9039,7 @@
       </c>
       <c r="L380" t="inlineStr">
         <is>
-          <t>O Impuro, Azrasizzle... o antigo deus maligno outrora selado pelos próprios deuses...!</t>
+          <t>O Impuro, Azrasizzle... o deus maligno antigo que um dia foi selado pelos próprios deuses...!</t>
         </is>
       </c>
     </row>
@@ -9094,9 +9069,9 @@
       </c>
       <c r="L381" t="inlineStr">
         <is>
-          <t>...Então essa é a verdadeira natureza da "Poça". Uma semente de calamidade pronta para brotar. Isso deve acabar aqui e agora.
-Heh... até um deus maligno provavelmente não consegue liberar todo o seu poder com um cheiro tão fresco grudado nele.
-Vamos, #pc. Deixo o resto com você!</t>
+          <t>...Então esta é a verdadeira natureza da "Poça". Uma semente de calamidade esperando para brotar. Deve acabar aqui e agora.
+Heh... nem um deus maligno, aposto, consegue liberar toda a sua força com um cheiro tão fresco colado nele.
+Vá, #pc. Deixo o resto com você!</t>
         </is>
       </c>
     </row>
@@ -9252,7 +9227,7 @@
       </c>
       <c r="L394" t="inlineStr">
         <is>
-          <t>Quando aquele monstro apareceu, achei que estávamos acabados... mas, no fim, as coisas têm um jeito de se resolver.</t>
+          <t>Quando aquele monstro apareceu, pensei que estávamos acabados... mas no fim, as coisas se ajeitam.</t>
         </is>
       </c>
     </row>
@@ -9280,8 +9255,8 @@
       </c>
       <c r="L395" t="inlineStr">
         <is>
-          <t>Issizzle... aquele miserável. Mesmo que a calamidade esteja longe no futuro, não acredito que ele liberaria algo assim por causa de sua ambição.
-Mas isso é preocupante. Agora não podemos cumprir nossa promessa a ele.</t>
+          <t>Issizzle... aquele desgraçado. Ainda que a calamidade esteja longe no futuro, não acredito que ele soltaria uma coisa dessas por causa da ambição dele.
+Mas isso é um problema. Agora não podemos cumprir a promessa com ele.</t>
         </is>
       </c>
     </row>
@@ -9335,8 +9310,8 @@
       </c>
       <c r="L397" t="inlineStr">
         <is>
-          <t>...Sim. Duvido que ele vá acreditar tão facilmente, mas é tudo o que podemos dizer.
-Tudo certo. Vamos voltar para a base e esperar por Issizzle.</t>
+          <t>...Sim. Duvido que ele acredite tão facilmente, mas é tudo o que podemos dizer.
+Muito bem. Voltemos à base e esperemos Issizzle.</t>
         </is>
       </c>
     </row>
@@ -9456,7 +9431,7 @@
       </c>
       <c r="L410" t="inlineStr">
         <is>
-          <t>Chaleira... posso falar com você?</t>
+          <t>Kettle... posso falar com você?</t>
         </is>
       </c>
     </row>
@@ -9506,7 +9481,7 @@
       </c>
       <c r="L412" t="inlineStr">
         <is>
-          <t>Antes... eu vi um garoto de manto preto que nunca tinha visto antes, só olhando para mim e Corgon. Então tentei falar com ele, mas Demitas apareceu todo furioso e começou a discutir com ele...</t>
+          <t>Mais cedo... vi um garoto num manto preto que eu nunca tinha visto, só ficando olhando para mim e para o Corgon. Então tentei falar com ele, mas o Demitas invadiu todo furioso e começou a discutir com ele...</t>
         </is>
       </c>
     </row>
@@ -9533,8 +9508,8 @@
       </c>
       <c r="L413" t="inlineStr">
         <is>
-          <t>Entendo... achei que ele apareceria por volta dessa hora.
-O garoto de preto é Sorin — a forma humana de Issizzle. Demitas e ele têm... um histórico complicado.</t>
+          <t>Entendo... Eu imaginava que ele apareceria por volta de agora.
+O garoto de preto é Sorin: a forma humana de Issizzle. Demitas e ele têm... um passado.</t>
         </is>
       </c>
     </row>
@@ -9586,8 +9561,8 @@
       </c>
       <c r="L415" t="inlineStr">
         <is>
-          <t>Não há nada a temer, Quruitzia. Mantivemos nossa promessa a ele na Cripta dos Condenados.
-Não é mesmo, Loytel?</t>
+          <t>Não há o que temer, Quruitzia. Cumprimos a promessa com ele na Cripta dos Condenados.
+Não é verdade, Loytel?</t>
         </is>
       </c>
     </row>
@@ -9612,7 +9587,7 @@
       </c>
       <c r="L416" t="inlineStr">
         <is>
-          <t>...Bem, Kettle...</t>
+          <t>...Bom, Kettle...</t>
         </is>
       </c>
     </row>
@@ -9662,7 +9637,7 @@
       </c>
       <c r="L418" t="inlineStr">
         <is>
-          <t>N-nada... Tenho certeza de que o perigo passou, mas por via das dúvidas, o que acontece se deixarmos o Issizzle irritado?</t>
+          <t>N-nada... Tenho certeza de que o perigo passou, mas só por precaução: o que acontece se deixarmos Issizzle com raiva?</t>
         </is>
       </c>
     </row>
@@ -9689,8 +9664,8 @@
       </c>
       <c r="L419" t="inlineStr">
         <is>
-          <t>Ele é um feiticeiro poderoso o suficiente para dizimar um reino inteiro. Nesta era, ele certamente é uma das últimas pessoas que queremos provocar.
-Mas não se preocupe, Loytel. Porque &lt;b&gt;se você tivesse feito algo para irritá-lo&lt;/b&gt;, já estaria dormindo debaixo da terra, hehe.</t>
+          <t>Ele é um feiticeiro poderoso o bastante para apagar um reino inteiro. Nesta era, é certamente uma das últimas pessoas que queremos provocar.
+Mas não se preocupe, Loytel. Porque &lt;b&gt;se você tivesse feito qualquer coisa para irritá-lo&lt;/b&gt;, já estaria dormindo embaixo da terra, hehe.</t>
         </is>
       </c>
     </row>
@@ -9740,7 +9715,7 @@
       </c>
       <c r="L421" t="inlineStr">
         <is>
-          <t>(sussurro) Lady Farris—o que quer que tenha acontecido na "Poça", devemos esconder isso dele a todo custo. Até a Kettle já está desconfiada.</t>
+          <t>(sussurro) Lady Farris: o que quer que tenha acontecido na "Poça", temos de esconder dele absolutamente. Até o Kettle já está desconfiando.</t>
         </is>
       </c>
     </row>
@@ -9765,7 +9740,7 @@
       </c>
       <c r="L422" t="inlineStr">
         <is>
-          <t>(sussurro) Sim, Lorde Loytel... É uma pena não podermos transformar isso em uma canção, mas não há o que fazer desta vez.</t>
+          <t>(sussurro) Sim, Lorde Loytel... É uma pena que não possamos transformar em canção, mas desta vez não dá.</t>
         </is>
       </c>
     </row>
@@ -9790,7 +9765,7 @@
       </c>
       <c r="L423" t="inlineStr">
         <is>
-          <t>...Tudo certo. O Demitas provavelmente já se acalmou. Vamos ouvir o que ele tem a dizer.</t>
+          <t>...Muito bem. O Demitas provavelmente já esfriou. Vamos ouvir o que ele tem a dizer.</t>
         </is>
       </c>
     </row>
@@ -9889,8 +9864,8 @@
       </c>
       <c r="L430" t="inlineStr">
         <is>
-          <t>...Então podemos presumir que a promessa foi cumprida sem incidentes?
-Não, é apenas uma confirmação. Percebi a interferência na "Poça" imediatamente. Porém...</t>
+          <t>...Então podemos assumir que a promessa foi cumprida sem incidentes?
+Não, é só uma confirmação. Senti a interferência na "Poça" de imediato. Porém...</t>
         </is>
       </c>
     </row>
@@ -9946,9 +9921,9 @@
       </c>
       <c r="L432" t="inlineStr">
         <is>
-          <t>A partir daquele momento, uma parte da minha magia foi perdida. Para ser exato, perdi o corpo imortal do Issizzle.
-Heh, mas isso, por si só, é uma prova bem-vinda de que a "Poça" começou a se agitar novamente.
-Não há motivo para preocupação. À medida que o poder daquele ser cresce dentro da "Poça", minha própria magia também retornará.</t>
+          <t>Desde aquele momento, uma parte da minha magia se perdeu. Para ser preciso, perdi o corpo imortal de Issizzle.
+Heh, mas isso, em si, é a prova mais bem-vinda de que a "Poça" voltou a se agitar.
+Não há com o que se preocupar. Conforme o poder daquele ser cresce na "Poça", minha própria magia também voltará.</t>
         </is>
       </c>
     </row>
@@ -10002,8 +9977,8 @@
       </c>
       <c r="L434" t="inlineStr">
         <is>
-          <t>Você perdeu parte do seu poder? Isso é maravilh— não, isso é terrível!
-Então isso significa que o Corgon e a Quruitzia não estão mais em perigo?</t>
+          <t>Você perdeu parte do seu poder? Isso é ótim... quer dizer, que terrível!
+Então quer dizer que Corgon e Quruitzia já não estão em perigo?</t>
         </is>
       </c>
     </row>
@@ -10031,8 +10006,8 @@
       </c>
       <c r="L435" t="inlineStr">
         <is>
-          <t>…Mestre, seria bom que explicasse isso direito mais tarde, para que até mesmo o tolo aqui presente entenda o peso das palavras de um mago.
-Decidi manter minha promessa, mesmo que ainda possua a magia para transformar este lugar em um cenário de devastação neste exato momento, sem outro motivo além deste tolo me desagradar.</t>
+          <t>…Mestre, seria bom explicares direito depois, para que até o tolo que está aqui entenda o quanto as palavras pesam para um mago.
+Decidi cumprir minha promessa, mesmo que eu ainda possua a magia para transformar este lugar num cenário de devastação neste exato momento, por nenhum motivo além daquele tolo me desagradar.</t>
         </is>
       </c>
     </row>
@@ -10062,9 +10037,9 @@
       </c>
       <c r="L436" t="inlineStr">
         <is>
-          <t>...Não importa. De qualquer forma, duvido que eu vá encontrar a maioria dos presentes aqui novamente.
-Ter visto curiosidades como uma criança dragão e uma bruxa, e compartilhado uma troca tão cordial com um velho amigo, suponho que valeu a pena o trabalho de vir.
-Agora então, Mestre.</t>
+          <t>...Tanto faz. De qualquer forma, duvido que volte a encontrar a maioria dos presentes.
+Ter visto curiosidades como um filhote de dragão e uma bruxa, e ter partilhado um intercâmbio tão cordial com um velho amigo, acho que valeu o trabalho de vir.
+Pois bem, Mestre.</t>
         </is>
       </c>
     </row>
@@ -10080,19 +10055,19 @@
       </c>
       <c r="J437" s="26" t="inlineStr">
         <is>
-          <t>…ソリン、その身体であの古城に帰る気かい？
+          <t>…ソリン、その身体であの古塔に帰る気かい？
 悪気はないけど、この前訪れた時は、とても「人間」がくつろげる場所だとは思えなかったよ。</t>
         </is>
       </c>
       <c r="K437" s="25" t="inlineStr">
         <is>
-          <t>...Sorin, are you really going back to that old castle in your...current body?
+          <t>...Sorin, are you really going back to that old tower in your...current body?
 No offense, but last time I visited your castle, it hardly felt like a place a "human" could relax.</t>
         </is>
       </c>
       <c r="L437" t="inlineStr">
         <is>
-          <t>...Sorin, você realmente vai voltar para aquele velho castelo no seu... corpo atual?
+          <t>...Sorin, você vai mesmo voltar para aquela torre velha no seu... corpo atual?
 Sem ofensa, mas da última vez que visitei seu castelo, mal parecia um lugar onde um "humano" pudesse relaxar.</t>
         </is>
       </c>
@@ -10148,7 +10123,7 @@
       <c r="L439" t="inlineStr">
         <is>
           <t xml:space="preserve">Hehe, não faça essa cara assustadora. Deixa eu dizer de outro jeito.
-Por que não viver aqui conosco até sua magia voltar, Sorin? </t>
+Que tal morar aqui conosco até sua magia voltar, Sorin? </t>
         </is>
       </c>
     </row>
@@ -10280,8 +10255,8 @@
       </c>
       <c r="L444" t="inlineStr">
         <is>
-          <t>...E uma que me é bastante conveniente.
-O significado por trás do encontro da criança dragão e da bruxa, do aventureiro atraído pelos fios do destino e, acima de tudo, Mestre—desde que descobri o segredo da pedra mágica, sua própria existência se recusa a soltar minha curiosidade.</t>
+          <t>...E uma que me é bem conveniente.
+O significado por trás do encontro do filhote de dragão e da bruxa, o aventureiro atraído pelos fios do destino, e acima de tudo, Mestre: desde que aprendi o segredo da pedra mágica, a sua própria existência se recusa a soltar minha curiosidade.</t>
         </is>
       </c>
     </row>
@@ -10309,8 +10284,8 @@
       </c>
       <c r="L445" t="inlineStr">
         <is>
-          <t>Claro, não tenho intenção de me hospedar de graça.
-O que desejaria em troca? Um grimório perdido da era antiga, um elixir da imortalidade ou talvez um exército de mortos que nunca se cansa de trabalhar?</t>
+          <t>Claro, não tenho intenção de ficar de graça.
+O que desejaria em troca? Um grimório perdido da era antiga, um elixir da imortalidade, ou talvez um exército de mortos que nunca se cansa de trabalhar?</t>
         </is>
       </c>
     </row>
@@ -10340,9 +10315,9 @@
       </c>
       <c r="L446" t="inlineStr">
         <is>
-          <t>Bem, acho que pelo menos posso pedir que conserte os potes que Corgon destruiu.
-Mas, independentemente disso, dou as boas-vindas à sua estadia aqui.
-E Sorin, se ainda me chama de Mestre, lembre-se. Ainda temos muito a aprender com este mundo, não importa quanto tempo nossas vidas durem.</t>
+          <t xml:space="preserve">Bom, acho que vou pelo menos pedir para consertar as panelas que o Corgon espatifou.
+Mas, de todo modo, recebo sua estadia de braços abertos.
+E Sorin, se ainda me chama de Mestre, lembre: ainda temos muito a aprender com este mundo, por mais longas que sejam nossas vidas. </t>
         </is>
       </c>
     </row>
